--- a/inst/resources/reference_indicator_bank.xlsx
+++ b/inst/resources/reference_indicator_bank.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5854DA1-146B-4CCA-B36D-B57E927B205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D08088C-6D28-4F59-94C4-2C9D6DFDD41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_bank" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_bank!$A$1:$J$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_bank!$A$1:$K$350</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="876">
   <si>
     <t>indicator_name</t>
   </si>
@@ -2641,6 +2641,39 @@
   </si>
   <si>
     <t>Proportion of households with less than 15 liters of all purpose water per person per day.</t>
+  </si>
+  <si>
+    <t>5-year age bins</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Key Informant Type</t>
+  </si>
+  <si>
+    <t>Sex, Reported  Cause of Death, Reported Location of Death</t>
+  </si>
+  <si>
+    <t>Sex, Age in Months</t>
+  </si>
+  <si>
+    <t>Pregnancy and Lactation Status</t>
+  </si>
+  <si>
+    <t>Soap Ownership</t>
+  </si>
+  <si>
+    <t>Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
+  </si>
+  <si>
+    <t>disaggregation</t>
+  </si>
+  <si>
+    <t>Main Food Sources, Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
+  </si>
+  <si>
+    <t>Main Water Source, Barriers to Water Access, Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
   </si>
 </sst>
 </file>
@@ -3038,23 +3071,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F55F414-FB28-4448-AE5F-D8C818819F2A}">
-  <dimension ref="A1:M350"/>
+  <dimension ref="A1:N350"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="4" width="22.7109375" customWidth="1"/>
     <col min="5" max="5" width="78.28515625" customWidth="1"/>
-    <col min="6" max="6" width="69.28515625" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" customWidth="1"/>
-    <col min="8" max="8" width="47.42578125" customWidth="1"/>
-    <col min="9" max="9" width="51.7109375" customWidth="1"/>
-    <col min="10" max="10" width="46.28515625" customWidth="1"/>
-    <col min="11" max="12" width="19" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="69.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="47.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="51.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="51.7109375" customWidth="1"/>
+    <col min="11" max="11" width="46.28515625" customWidth="1"/>
+    <col min="12" max="13" width="19" style="4" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -3083,19 +3117,22 @@
         <v>11</v>
       </c>
       <c r="J1" t="s">
+        <v>873</v>
+      </c>
+      <c r="K1" t="s">
         <v>106</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -3123,8 +3160,8 @@
       <c r="I2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>91</v>
+      <c r="J2" s="2" t="s">
+        <v>865</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>91</v>
@@ -3132,8 +3169,11 @@
       <c r="M2" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N2" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>101</v>
       </c>
@@ -3161,8 +3201,8 @@
       <c r="I3" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>91</v>
+      <c r="J3" s="2" t="s">
+        <v>866</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>91</v>
@@ -3170,8 +3210,11 @@
       <c r="M3" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>101</v>
       </c>
@@ -3199,8 +3242,8 @@
       <c r="I4" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>91</v>
+      <c r="J4" s="2" t="s">
+        <v>866</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>91</v>
@@ -3208,8 +3251,11 @@
       <c r="M4" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N4" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>101</v>
       </c>
@@ -3237,17 +3283,17 @@
       <c r="I5" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L5" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>101</v>
       </c>
@@ -3275,17 +3321,17 @@
       <c r="I6" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L6" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>101</v>
       </c>
@@ -3313,8 +3359,8 @@
       <c r="I7" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>91</v>
+      <c r="J7" s="2" t="s">
+        <v>866</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>91</v>
@@ -3322,8 +3368,11 @@
       <c r="M7" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>101</v>
       </c>
@@ -3351,8 +3400,8 @@
       <c r="I8" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>91</v>
+      <c r="J8" s="2" t="s">
+        <v>866</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>91</v>
@@ -3360,8 +3409,11 @@
       <c r="M8" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N8" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>101</v>
       </c>
@@ -3389,17 +3441,17 @@
       <c r="I9" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N9" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>101</v>
       </c>
@@ -3427,17 +3479,17 @@
       <c r="I10" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N10" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>102</v>
       </c>
@@ -3465,17 +3517,17 @@
       <c r="I11" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L11" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>102</v>
       </c>
@@ -3503,17 +3555,17 @@
       <c r="I12" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>102</v>
       </c>
@@ -3541,17 +3593,17 @@
       <c r="I13" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L13" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>102</v>
       </c>
@@ -3579,17 +3631,17 @@
       <c r="I14" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>102</v>
       </c>
@@ -3617,17 +3669,17 @@
       <c r="I15" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>103</v>
       </c>
@@ -3655,17 +3707,17 @@
       <c r="I16" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L16" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>103</v>
       </c>
@@ -3693,20 +3745,20 @@
       <c r="I17" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>103</v>
       </c>
@@ -3734,17 +3786,17 @@
       <c r="I18" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N18" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>103</v>
       </c>
@@ -3772,17 +3824,17 @@
       <c r="I19" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L19" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N19" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>103</v>
       </c>
@@ -3810,17 +3862,17 @@
       <c r="I20" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>103</v>
       </c>
@@ -3848,17 +3900,17 @@
       <c r="I21" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N21" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>103</v>
       </c>
@@ -3886,17 +3938,17 @@
       <c r="I22" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N22" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>103</v>
       </c>
@@ -3925,19 +3977,22 @@
         <v>659</v>
       </c>
       <c r="J23" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="N23" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>103</v>
       </c>
@@ -3966,19 +4021,22 @@
         <v>659</v>
       </c>
       <c r="J24" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>103</v>
       </c>
@@ -4007,19 +4065,22 @@
         <v>659</v>
       </c>
       <c r="J25" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L25" s="3">
+      <c r="M25" s="3">
         <v>30</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="N25" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>103</v>
       </c>
@@ -4048,19 +4109,22 @@
         <v>659</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>50</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="N26" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>103</v>
       </c>
@@ -4089,19 +4153,22 @@
         <v>659</v>
       </c>
       <c r="J27" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="N27" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>103</v>
       </c>
@@ -4130,19 +4197,22 @@
         <v>659</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L28" s="3">
+      <c r="M28" s="3">
         <v>15</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="N28" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>103</v>
       </c>
@@ -4171,19 +4241,22 @@
         <v>659</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>30</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>103</v>
       </c>
@@ -4212,19 +4285,22 @@
         <v>659</v>
       </c>
       <c r="J30" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L30" s="3">
+      <c r="M30" s="3">
         <v>50</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="N30" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>103</v>
       </c>
@@ -4253,19 +4329,22 @@
         <v>659</v>
       </c>
       <c r="J31" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="L31" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L31" s="3">
+      <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="N31" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>103</v>
       </c>
@@ -4294,19 +4373,22 @@
         <v>659</v>
       </c>
       <c r="J32" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="N32" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>103</v>
       </c>
@@ -4335,19 +4417,22 @@
         <v>659</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30</v>
       </c>
-      <c r="M33" s="3" t="s">
+      <c r="N33" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>103</v>
       </c>
@@ -4376,19 +4461,22 @@
         <v>659</v>
       </c>
       <c r="J34" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L34" s="3">
+      <c r="M34" s="3">
         <v>50</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="N34" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>103</v>
       </c>
@@ -4417,19 +4505,22 @@
         <v>659</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K35" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="L35" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="N35" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>103</v>
       </c>
@@ -4458,19 +4549,22 @@
         <v>659</v>
       </c>
       <c r="J36" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L36" s="3">
+      <c r="M36" s="3">
         <v>15</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="N36" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>103</v>
       </c>
@@ -4499,19 +4593,22 @@
         <v>659</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L37" s="3">
+      <c r="M37" s="3">
         <v>30</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="N37" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>103</v>
       </c>
@@ -4540,19 +4637,22 @@
         <v>659</v>
       </c>
       <c r="J38" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L38" s="3">
+      <c r="M38" s="3">
         <v>50</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="N38" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>104</v>
       </c>
@@ -4580,17 +4680,17 @@
       <c r="I39" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="K39" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L39" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N39" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>104</v>
       </c>
@@ -4618,17 +4718,17 @@
       <c r="I40" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L40" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N40" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>104</v>
       </c>
@@ -4657,19 +4757,22 @@
         <v>659</v>
       </c>
       <c r="J41" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K41" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N41" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>105</v>
       </c>
@@ -4697,17 +4800,20 @@
       <c r="I42" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="J42" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
+      <c r="N42" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>105</v>
       </c>
@@ -4735,17 +4841,20 @@
       <c r="I43" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="K43" s="3" t="s">
+      <c r="J43" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>0.5</v>
       </c>
-      <c r="M43" s="3" t="s">
+      <c r="N43" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>105</v>
       </c>
@@ -4773,17 +4882,20 @@
       <c r="I44" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="J44" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="N44" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>105</v>
       </c>
@@ -4811,17 +4923,20 @@
       <c r="I45" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="J45" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>105</v>
       </c>
@@ -4849,17 +4964,20 @@
       <c r="I46" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="J46" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3" t="s">
+      <c r="N46" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>105</v>
       </c>
@@ -4887,17 +5005,20 @@
       <c r="I47" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="J47" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="N47" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>105</v>
       </c>
@@ -4925,17 +5046,20 @@
       <c r="I48" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="J48" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="N48" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>105</v>
       </c>
@@ -4963,17 +5087,20 @@
       <c r="I49" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="J49" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="N49" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>105</v>
       </c>
@@ -5001,13 +5128,13 @@
       <c r="I50" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="K50" s="3"/>
       <c r="L50" s="3"/>
-      <c r="M50" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="3"/>
+      <c r="N50" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>106</v>
       </c>
@@ -5035,17 +5162,20 @@
       <c r="I51" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K51" s="3" t="s">
+      <c r="J51" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L51" s="3">
+      <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="5" t="s">
+      <c r="N51" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>106</v>
       </c>
@@ -5073,17 +5203,20 @@
       <c r="I52" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="J52" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10</v>
       </c>
-      <c r="M52" s="5" t="s">
+      <c r="N52" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>106</v>
       </c>
@@ -5111,17 +5244,20 @@
       <c r="I53" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="J53" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L53" s="3">
+      <c r="M53" s="3">
         <v>20</v>
       </c>
-      <c r="M53" s="5" t="s">
+      <c r="N53" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>106</v>
       </c>
@@ -5149,17 +5285,20 @@
       <c r="I54" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="J54" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L54" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30</v>
       </c>
-      <c r="M54" s="5" t="s">
+      <c r="N54" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>106</v>
       </c>
@@ -5188,19 +5327,22 @@
         <v>659</v>
       </c>
       <c r="J55" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K55" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K55" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="L55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N55" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>106</v>
       </c>
@@ -5229,19 +5371,22 @@
         <v>659</v>
       </c>
       <c r="J56" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K56" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="L56" s="5" t="s">
         <v>91</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N56" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>106</v>
       </c>
@@ -5270,19 +5415,22 @@
         <v>659</v>
       </c>
       <c r="J57" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K57" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K57" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="L57" s="5" t="s">
         <v>91</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N57" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>106</v>
       </c>
@@ -5310,17 +5458,17 @@
       <c r="I58" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="L58" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="5" t="s">
+      <c r="N58" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="59" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>106</v>
       </c>
@@ -5348,17 +5496,17 @@
       <c r="I59" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="5" t="s">
+      <c r="N59" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>106</v>
       </c>
@@ -5386,17 +5534,17 @@
       <c r="I60" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="L60" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="5" t="s">
+      <c r="N60" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>106</v>
       </c>
@@ -5424,17 +5572,17 @@
       <c r="I61" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="L61" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="5" t="s">
+      <c r="N61" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>106</v>
       </c>
@@ -5462,17 +5610,17 @@
       <c r="I62" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="L62" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="5" t="s">
+      <c r="N62" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>106</v>
       </c>
@@ -5500,17 +5648,17 @@
       <c r="I63" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="L63" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L63" s="3">
+      <c r="M63" s="3">
         <v>50</v>
       </c>
-      <c r="M63" s="5" t="s">
+      <c r="N63" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>106</v>
       </c>
@@ -5538,17 +5686,17 @@
       <c r="I64" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="L64" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L64" s="3">
+      <c r="M64" s="3">
         <v>100</v>
       </c>
-      <c r="M64" s="5" t="s">
+      <c r="N64" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>106</v>
       </c>
@@ -5576,17 +5724,17 @@
       <c r="I65" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="L65" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L65" s="3">
+      <c r="M65" s="3">
         <v>200</v>
       </c>
-      <c r="M65" s="5" t="s">
+      <c r="N65" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>106</v>
       </c>
@@ -5614,17 +5762,17 @@
       <c r="I66" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="L66" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>0</v>
       </c>
-      <c r="M66" s="5" t="s">
+      <c r="N66" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>106</v>
       </c>
@@ -5652,17 +5800,17 @@
       <c r="I67" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="L67" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L67" s="3">
+      <c r="M67" s="3">
         <v>25</v>
       </c>
-      <c r="M67" s="5" t="s">
+      <c r="N67" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>106</v>
       </c>
@@ -5690,17 +5838,17 @@
       <c r="I68" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="L68" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L68" s="3">
+      <c r="M68" s="3">
         <v>50</v>
       </c>
-      <c r="M68" s="5" t="s">
+      <c r="N68" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>106</v>
       </c>
@@ -5728,17 +5876,17 @@
       <c r="I69" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="L69" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L69" s="3">
+      <c r="M69" s="3">
         <v>100</v>
       </c>
-      <c r="M69" s="5" t="s">
+      <c r="N69" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>106</v>
       </c>
@@ -5766,17 +5914,17 @@
       <c r="I70" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K70" s="3" t="s">
+      <c r="L70" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="5" t="s">
+      <c r="N70" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>106</v>
       </c>
@@ -5804,17 +5952,17 @@
       <c r="I71" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="L71" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L71" s="3">
+      <c r="M71" s="3">
         <v>50</v>
       </c>
-      <c r="M71" s="5" t="s">
+      <c r="N71" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>106</v>
       </c>
@@ -5842,17 +5990,17 @@
       <c r="I72" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="L72" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>100</v>
       </c>
-      <c r="M72" s="5" t="s">
+      <c r="N72" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>106</v>
       </c>
@@ -5880,17 +6028,17 @@
       <c r="I73" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="L73" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L73" s="3">
+      <c r="M73" s="3">
         <v>200</v>
       </c>
-      <c r="M73" s="5" t="s">
+      <c r="N73" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>106</v>
       </c>
@@ -5918,17 +6066,17 @@
       <c r="I74" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L74" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M74" s="5" t="s">
+      <c r="M74" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N74" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>106</v>
       </c>
@@ -5956,17 +6104,17 @@
       <c r="I75" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="K75" s="3" t="s">
+      <c r="L75" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L75" s="3" t="s">
+      <c r="M75" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="M75" s="3" t="s">
+      <c r="N75" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>106</v>
       </c>
@@ -5994,17 +6142,17 @@
       <c r="I76" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="K76" s="3" t="s">
+      <c r="L76" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L76" s="3" t="s">
+      <c r="M76" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="M76" s="3" t="s">
+      <c r="N76" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>106</v>
       </c>
@@ -6032,17 +6180,17 @@
       <c r="I77" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="L77" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L77" s="3" t="s">
+      <c r="M77" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="M77" s="3" t="s">
+      <c r="N77" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>106</v>
       </c>
@@ -6070,17 +6218,17 @@
       <c r="I78" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="L78" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L78" s="3">
+      <c r="M78" s="3">
         <v>0</v>
       </c>
-      <c r="M78" s="5" t="s">
+      <c r="N78" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>106</v>
       </c>
@@ -6108,17 +6256,17 @@
       <c r="I79" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K79" s="3" t="s">
+      <c r="L79" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L79" s="3">
+      <c r="M79" s="3">
         <v>100</v>
       </c>
-      <c r="M79" s="5" t="s">
+      <c r="N79" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>106</v>
       </c>
@@ -6146,17 +6294,17 @@
       <c r="I80" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="L80" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L80" s="3">
+      <c r="M80" s="3">
         <v>200</v>
       </c>
-      <c r="M80" s="5" t="s">
+      <c r="N80" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>106</v>
       </c>
@@ -6184,17 +6332,17 @@
       <c r="I81" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="L81" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="5" t="s">
+      <c r="N81" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>106</v>
       </c>
@@ -6222,17 +6370,17 @@
       <c r="I82" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K82" s="3" t="s">
+      <c r="L82" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L82" s="3">
+      <c r="M82" s="3">
         <v>0</v>
       </c>
-      <c r="M82" s="5" t="s">
+      <c r="N82" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>106</v>
       </c>
@@ -6260,17 +6408,17 @@
       <c r="I83" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>50</v>
       </c>
-      <c r="M83" s="5" t="s">
+      <c r="N83" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="84" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>106</v>
       </c>
@@ -6298,17 +6446,17 @@
       <c r="I84" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K84" s="3" t="s">
+      <c r="L84" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L84" s="3">
+      <c r="M84" s="3">
         <v>100</v>
       </c>
-      <c r="M84" s="5" t="s">
+      <c r="N84" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="85" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>106</v>
       </c>
@@ -6336,17 +6484,17 @@
       <c r="I85" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="K85" s="3" t="s">
+      <c r="L85" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L85" s="3">
+      <c r="M85" s="3">
         <v>200</v>
       </c>
-      <c r="M85" s="5" t="s">
+      <c r="N85" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>106</v>
       </c>
@@ -6374,17 +6522,17 @@
       <c r="I86" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="K86" s="3" t="s">
+      <c r="L86" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L86" s="3">
+      <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="5" t="s">
+      <c r="N86" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>106</v>
       </c>
@@ -6412,17 +6560,17 @@
       <c r="I87" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="K87" s="3" t="s">
+      <c r="L87" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L87" s="3">
+      <c r="M87" s="3">
         <v>20</v>
       </c>
-      <c r="M87" s="5" t="s">
+      <c r="N87" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="88" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>106</v>
       </c>
@@ -6450,17 +6598,17 @@
       <c r="I88" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="K88" s="3" t="s">
+      <c r="L88" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L88" s="3">
+      <c r="M88" s="3">
         <v>30</v>
       </c>
-      <c r="M88" s="5" t="s">
+      <c r="N88" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>106</v>
       </c>
@@ -6488,17 +6636,17 @@
       <c r="I89" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40</v>
       </c>
-      <c r="M89" s="5" t="s">
+      <c r="N89" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>106</v>
       </c>
@@ -6526,17 +6674,20 @@
       <c r="I90" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="K90" s="3" t="s">
+      <c r="J90" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L90" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L90" s="3">
+      <c r="M90" s="3">
         <v>0</v>
       </c>
-      <c r="M90" s="5" t="s">
+      <c r="N90" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>106</v>
       </c>
@@ -6564,17 +6715,20 @@
       <c r="I91" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="J91" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L91" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>20</v>
       </c>
-      <c r="M91" s="5" t="s">
+      <c r="N91" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="92" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>106</v>
       </c>
@@ -6602,17 +6756,20 @@
       <c r="I92" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="K92" s="3" t="s">
+      <c r="J92" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L92" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L92" s="3">
+      <c r="M92" s="3">
         <v>40</v>
       </c>
-      <c r="M92" s="5" t="s">
+      <c r="N92" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>106</v>
       </c>
@@ -6640,17 +6797,20 @@
       <c r="I93" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="K93" s="3" t="s">
+      <c r="J93" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L93" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L93" s="3">
+      <c r="M93" s="3">
         <v>50</v>
       </c>
-      <c r="M93" s="5" t="s">
+      <c r="N93" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>107</v>
       </c>
@@ -6678,17 +6838,20 @@
       <c r="I94" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="J94" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L94" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>107</v>
       </c>
@@ -6716,17 +6879,20 @@
       <c r="I95" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K95" s="3" t="s">
+      <c r="J95" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L95" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L95" s="3">
+      <c r="M95" s="3">
         <v>5</v>
       </c>
-      <c r="M95" s="3" t="s">
+      <c r="N95" s="3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="96" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>107</v>
       </c>
@@ -6754,17 +6920,20 @@
       <c r="I96" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="J96" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>10</v>
       </c>
-      <c r="M96" s="3" t="s">
+      <c r="N96" s="3" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>107</v>
       </c>
@@ -6792,17 +6961,20 @@
       <c r="I97" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K97" s="3" t="s">
+      <c r="J97" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L97" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L97" s="3">
+      <c r="M97" s="3">
         <v>15</v>
       </c>
-      <c r="M97" s="3" t="s">
+      <c r="N97" s="3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>107</v>
       </c>
@@ -6830,17 +7002,20 @@
       <c r="I98" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="K98" s="3" t="s">
+      <c r="J98" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="L98" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L98" s="3">
+      <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3" t="s">
+      <c r="N98" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>107</v>
       </c>
@@ -6868,17 +7043,20 @@
       <c r="I99" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="J99" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="L99" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L99" s="3">
+      <c r="M99" s="3">
         <v>10</v>
       </c>
-      <c r="M99" s="3" t="s">
+      <c r="N99" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="100" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>107</v>
       </c>
@@ -6906,17 +7084,20 @@
       <c r="I100" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="J100" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>20</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>107</v>
       </c>
@@ -6944,17 +7125,20 @@
       <c r="I101" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="J101" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="L101" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>30</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>107</v>
       </c>
@@ -6982,17 +7166,17 @@
       <c r="I102" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K102" s="3" t="s">
+      <c r="L102" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L102" s="3" t="s">
+      <c r="M102" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="M102" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>107</v>
       </c>
@@ -7020,17 +7204,17 @@
       <c r="I103" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="L103" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L103" s="3" t="s">
+      <c r="M103" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="M103" s="3" t="s">
+      <c r="N103" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>107</v>
       </c>
@@ -7058,17 +7242,17 @@
       <c r="I104" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K104" s="3" t="s">
+      <c r="L104" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L104" s="3" t="s">
+      <c r="M104" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="M104" s="3" t="s">
+      <c r="N104" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>107</v>
       </c>
@@ -7096,17 +7280,20 @@
       <c r="I105" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K105" s="3" t="s">
+      <c r="J105" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L105" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="L105" s="3">
+      <c r="M105" s="3">
         <v>0</v>
       </c>
-      <c r="M105" s="3" t="s">
+      <c r="N105" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>107</v>
       </c>
@@ -7134,17 +7321,20 @@
       <c r="I106" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K106" s="3" t="s">
+      <c r="J106" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L106" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L106" s="3">
+      <c r="M106" s="3">
         <v>5</v>
       </c>
-      <c r="M106" s="3" t="s">
+      <c r="N106" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -7172,17 +7362,20 @@
       <c r="I107" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K107" s="3" t="s">
+      <c r="J107" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L107" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L107" s="3">
+      <c r="M107" s="3">
         <v>10</v>
       </c>
-      <c r="M107" s="3" t="s">
+      <c r="N107" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="108" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -7210,17 +7403,20 @@
       <c r="I108" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K108" s="3" t="s">
+      <c r="J108" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L108" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L108" s="3">
+      <c r="M108" s="3">
         <v>15</v>
       </c>
-      <c r="M108" s="3" t="s">
+      <c r="N108" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -7248,17 +7444,20 @@
       <c r="I109" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K109" s="3" t="s">
+      <c r="J109" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L109" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L109" s="3">
+      <c r="M109" s="3">
         <v>30</v>
       </c>
-      <c r="M109" s="3" t="s">
+      <c r="N109" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>107</v>
       </c>
@@ -7286,17 +7485,17 @@
       <c r="I110" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K110" s="3" t="s">
+      <c r="L110" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L110" s="3">
+      <c r="M110" s="3">
         <v>0</v>
       </c>
-      <c r="M110" s="3" t="s">
+      <c r="N110" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>107</v>
       </c>
@@ -7324,17 +7523,17 @@
       <c r="I111" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K111" s="3" t="s">
+      <c r="L111" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L111" s="3">
+      <c r="M111" s="3">
         <v>20</v>
       </c>
-      <c r="M111" s="3" t="s">
+      <c r="N111" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>107</v>
       </c>
@@ -7362,17 +7561,17 @@
       <c r="I112" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K112" s="3" t="s">
+      <c r="L112" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L112" s="3">
+      <c r="M112" s="3">
         <v>30</v>
       </c>
-      <c r="M112" s="3" t="s">
+      <c r="N112" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>107</v>
       </c>
@@ -7400,17 +7599,17 @@
       <c r="I113" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K113" s="3" t="s">
+      <c r="L113" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L113" s="3">
+      <c r="M113" s="3">
         <v>45</v>
       </c>
-      <c r="M113" s="3" t="s">
+      <c r="N113" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>108</v>
       </c>
@@ -7439,19 +7638,22 @@
         <v>374</v>
       </c>
       <c r="J114" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K114" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="K114" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L114" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M114" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N114" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>108</v>
       </c>
@@ -7480,19 +7682,22 @@
         <v>375</v>
       </c>
       <c r="J115" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K115" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="K115" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L115" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M115" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N115" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>109</v>
       </c>
@@ -7520,8 +7725,8 @@
       <c r="I116" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="K116" s="3" t="s">
-        <v>91</v>
+      <c r="J116" s="2" t="s">
+        <v>875</v>
       </c>
       <c r="L116" s="3" t="s">
         <v>91</v>
@@ -7529,8 +7734,11 @@
       <c r="M116" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N116" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>109</v>
       </c>
@@ -7558,17 +7766,20 @@
       <c r="I117" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="K117" s="3" t="s">
+      <c r="J117" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="L117" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L117" s="3">
+      <c r="M117" s="3">
         <v>10</v>
       </c>
-      <c r="M117" s="3" t="s">
+      <c r="N117" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>109</v>
       </c>
@@ -7596,17 +7807,20 @@
       <c r="I118" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="K118" s="3" t="s">
+      <c r="J118" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="L118" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L118" s="3">
+      <c r="M118" s="3">
         <v>30</v>
       </c>
-      <c r="M118" s="3" t="s">
+      <c r="N118" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>109</v>
       </c>
@@ -7634,17 +7848,20 @@
       <c r="I119" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="K119" s="3" t="s">
+      <c r="J119" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="L119" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L119" s="3">
+      <c r="M119" s="3">
         <v>50</v>
       </c>
-      <c r="M119" s="3" t="s">
+      <c r="N119" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>109</v>
       </c>
@@ -7672,17 +7889,20 @@
       <c r="I120" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="K120" s="3" t="s">
+      <c r="J120" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="L120" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L120" s="3">
+      <c r="M120" s="3">
         <v>70</v>
       </c>
-      <c r="M120" s="3" t="s">
+      <c r="N120" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="121" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>110</v>
       </c>
@@ -7692,11 +7912,11 @@
       <c r="C121" s="1">
         <v>11001</v>
       </c>
-      <c r="K121" s="6"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
-    </row>
-    <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>111</v>
       </c>
@@ -7724,11 +7944,14 @@
       <c r="I122" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="K122" s="3"/>
+      <c r="J122" s="2" t="s">
+        <v>872</v>
+      </c>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
-    </row>
-    <row r="123" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N122" s="3"/>
+    </row>
+    <row r="123" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>111</v>
       </c>
@@ -7756,11 +7979,14 @@
       <c r="I123" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="K123" s="3"/>
+      <c r="J123" s="2" t="s">
+        <v>871</v>
+      </c>
       <c r="L123" s="3"/>
       <c r="M123" s="3"/>
-    </row>
-    <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N123" s="3"/>
+    </row>
+    <row r="124" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>111</v>
       </c>
@@ -7789,13 +8015,16 @@
         <v>659</v>
       </c>
       <c r="J124" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K124" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K124" s="3"/>
       <c r="L124" s="3"/>
       <c r="M124" s="3"/>
-    </row>
-    <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N124" s="3"/>
+    </row>
+    <row r="125" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>112</v>
       </c>
@@ -7823,11 +8052,11 @@
       <c r="I125" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="K125" s="3"/>
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
-    </row>
-    <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N125" s="3"/>
+    </row>
+    <row r="126" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>112</v>
       </c>
@@ -7855,11 +8084,11 @@
       <c r="I126" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="K126" s="3"/>
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
-    </row>
-    <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N126" s="3"/>
+    </row>
+    <row r="127" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>112</v>
       </c>
@@ -7887,11 +8116,11 @@
       <c r="I127" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="K127" s="3"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
-    </row>
-    <row r="128" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N127" s="3"/>
+    </row>
+    <row r="128" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>112</v>
       </c>
@@ -7919,11 +8148,11 @@
       <c r="I128" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="K128" s="3"/>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
-    </row>
-    <row r="129" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N128" s="3"/>
+    </row>
+    <row r="129" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>112</v>
       </c>
@@ -7951,11 +8180,11 @@
       <c r="I129" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="K129" s="3"/>
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
-    </row>
-    <row r="130" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N129" s="3"/>
+    </row>
+    <row r="130" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>112</v>
       </c>
@@ -7983,11 +8212,11 @@
       <c r="I130" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="K130" s="3"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
-    </row>
-    <row r="131" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N130" s="3"/>
+    </row>
+    <row r="131" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>113</v>
       </c>
@@ -8015,11 +8244,11 @@
       <c r="I131" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="K131" s="3"/>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
-    </row>
-    <row r="132" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N131" s="3"/>
+    </row>
+    <row r="132" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>113</v>
       </c>
@@ -8048,13 +8277,16 @@
         <v>659</v>
       </c>
       <c r="J132" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K132" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K132" s="3"/>
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
-    </row>
-    <row r="133" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N132" s="3"/>
+    </row>
+    <row r="133" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>113</v>
       </c>
@@ -8082,11 +8314,11 @@
       <c r="I133" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="K133" s="3"/>
       <c r="L133" s="3"/>
       <c r="M133" s="3"/>
-    </row>
-    <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N133" s="3"/>
+    </row>
+    <row r="134" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>113</v>
       </c>
@@ -8114,11 +8346,11 @@
       <c r="I134" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="K134" s="3"/>
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
-    </row>
-    <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N134" s="3"/>
+    </row>
+    <row r="135" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>113</v>
       </c>
@@ -8146,14 +8378,14 @@
       <c r="I135" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="K135" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K135" s="3"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
-    </row>
-    <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N135" s="3"/>
+    </row>
+    <row r="136" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>113</v>
       </c>
@@ -8181,14 +8413,14 @@
       <c r="I136" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="J136" s="2" t="s">
+      <c r="K136" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K136" s="3"/>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
-    </row>
-    <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N136" s="3"/>
+    </row>
+    <row r="137" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>113</v>
       </c>
@@ -8216,14 +8448,14 @@
       <c r="I137" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="J137" s="2" t="s">
+      <c r="K137" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K137" s="3"/>
       <c r="L137" s="3"/>
       <c r="M137" s="3"/>
-    </row>
-    <row r="138" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N137" s="3"/>
+    </row>
+    <row r="138" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>113</v>
       </c>
@@ -8251,14 +8483,14 @@
       <c r="I138" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="J138" s="2" t="s">
+      <c r="K138" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K138" s="3"/>
       <c r="L138" s="3"/>
       <c r="M138" s="3"/>
-    </row>
-    <row r="139" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N138" s="3"/>
+    </row>
+    <row r="139" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>113</v>
       </c>
@@ -8286,14 +8518,14 @@
       <c r="I139" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="J139" s="2" t="s">
+      <c r="K139" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K139" s="3"/>
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
-    </row>
-    <row r="140" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N139" s="3"/>
+    </row>
+    <row r="140" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>113</v>
       </c>
@@ -8321,14 +8553,14 @@
       <c r="I140" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="J140" s="2" t="s">
+      <c r="K140" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K140" s="3"/>
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
-    </row>
-    <row r="141" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N140" s="3"/>
+    </row>
+    <row r="141" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>113</v>
       </c>
@@ -8356,14 +8588,14 @@
       <c r="I141" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="J141" s="2" t="s">
+      <c r="K141" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K141" s="3"/>
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
-    </row>
-    <row r="142" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N141" s="3"/>
+    </row>
+    <row r="142" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>113</v>
       </c>
@@ -8391,14 +8623,14 @@
       <c r="I142" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="J142" s="2" t="s">
+      <c r="K142" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="K142" s="3"/>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
-    </row>
-    <row r="143" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N142" s="3"/>
+    </row>
+    <row r="143" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>113</v>
       </c>
@@ -8426,14 +8658,14 @@
       <c r="I143" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="J143" s="2" t="s">
+      <c r="K143" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K143" s="3"/>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
-    </row>
-    <row r="144" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N143" s="3"/>
+    </row>
+    <row r="144" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>113</v>
       </c>
@@ -8461,14 +8693,14 @@
       <c r="I144" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="J144" s="2" t="s">
+      <c r="K144" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K144" s="3"/>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
-    </row>
-    <row r="145" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N144" s="3"/>
+    </row>
+    <row r="145" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>113</v>
       </c>
@@ -8496,14 +8728,14 @@
       <c r="I145" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="J145" s="2" t="s">
+      <c r="K145" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K145" s="3"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
-    </row>
-    <row r="146" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N145" s="3"/>
+    </row>
+    <row r="146" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>113</v>
       </c>
@@ -8531,14 +8763,14 @@
       <c r="I146" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="K146" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K146" s="3"/>
       <c r="L146" s="3"/>
       <c r="M146" s="3"/>
-    </row>
-    <row r="147" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N146" s="3"/>
+    </row>
+    <row r="147" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>113</v>
       </c>
@@ -8566,14 +8798,14 @@
       <c r="I147" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="J147" s="2" t="s">
+      <c r="K147" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K147" s="3"/>
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
-    </row>
-    <row r="148" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N147" s="3"/>
+    </row>
+    <row r="148" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>113</v>
       </c>
@@ -8601,14 +8833,14 @@
       <c r="I148" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="J148" s="2" t="s">
+      <c r="K148" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K148" s="3"/>
       <c r="L148" s="3"/>
       <c r="M148" s="3"/>
-    </row>
-    <row r="149" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N148" s="3"/>
+    </row>
+    <row r="149" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>113</v>
       </c>
@@ -8636,14 +8868,14 @@
       <c r="I149" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="J149" s="2" t="s">
+      <c r="K149" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K149" s="3"/>
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
-    </row>
-    <row r="150" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N149" s="3"/>
+    </row>
+    <row r="150" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>113</v>
       </c>
@@ -8671,14 +8903,14 @@
       <c r="I150" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="J150" s="2" t="s">
+      <c r="K150" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="K150" s="3"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
-    </row>
-    <row r="151" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N150" s="3"/>
+    </row>
+    <row r="151" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>114</v>
       </c>
@@ -8706,11 +8938,14 @@
       <c r="I151" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="K151" s="3"/>
+      <c r="J151" s="2" t="s">
+        <v>874</v>
+      </c>
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
-    </row>
-    <row r="152" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N151" s="3"/>
+    </row>
+    <row r="152" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>114</v>
       </c>
@@ -8739,13 +8974,16 @@
         <v>640</v>
       </c>
       <c r="J152" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K152" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="K152" s="3"/>
       <c r="L152" s="3"/>
       <c r="M152" s="3"/>
-    </row>
-    <row r="153" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N152" s="3"/>
+    </row>
+    <row r="153" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>114</v>
       </c>
@@ -8774,13 +9012,16 @@
         <v>646</v>
       </c>
       <c r="J153" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K153" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="K153" s="3"/>
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
-    </row>
-    <row r="154" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N153" s="3"/>
+    </row>
+    <row r="154" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>114</v>
       </c>
@@ -8808,11 +9049,11 @@
       <c r="I154" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="K154" s="3"/>
       <c r="L154" s="3"/>
       <c r="M154" s="3"/>
-    </row>
-    <row r="155" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N154" s="3"/>
+    </row>
+    <row r="155" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>114</v>
       </c>
@@ -8840,11 +9081,11 @@
       <c r="I155" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="K155" s="3"/>
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
-    </row>
-    <row r="156" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N155" s="3"/>
+    </row>
+    <row r="156" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>114</v>
       </c>
@@ -8872,11 +9113,11 @@
       <c r="I156" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="K156" s="3"/>
       <c r="L156" s="3"/>
       <c r="M156" s="3"/>
-    </row>
-    <row r="157" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N156" s="3"/>
+    </row>
+    <row r="157" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>115</v>
       </c>
@@ -8904,11 +9145,14 @@
       <c r="I157" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="K157" s="3"/>
+      <c r="J157" s="2" t="s">
+        <v>874</v>
+      </c>
       <c r="L157" s="3"/>
       <c r="M157" s="3"/>
-    </row>
-    <row r="158" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N157" s="3"/>
+    </row>
+    <row r="158" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>115</v>
       </c>
@@ -8936,11 +9180,14 @@
       <c r="I158" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="K158" s="3"/>
+      <c r="J158" s="2" t="s">
+        <v>874</v>
+      </c>
       <c r="L158" s="3"/>
       <c r="M158" s="3"/>
-    </row>
-    <row r="159" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N158" s="3"/>
+    </row>
+    <row r="159" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>115</v>
       </c>
@@ -8968,11 +9215,14 @@
       <c r="I159" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="K159" s="3"/>
+      <c r="J159" s="2" t="s">
+        <v>874</v>
+      </c>
       <c r="L159" s="3"/>
       <c r="M159" s="3"/>
-    </row>
-    <row r="160" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N159" s="3"/>
+    </row>
+    <row r="160" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>115</v>
       </c>
@@ -9000,11 +9250,14 @@
       <c r="I160" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="K160" s="3"/>
+      <c r="J160" s="2" t="s">
+        <v>874</v>
+      </c>
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
-    </row>
-    <row r="161" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N160" s="3"/>
+    </row>
+    <row r="161" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>116</v>
       </c>
@@ -9014,11 +9267,11 @@
       <c r="C161" s="1">
         <v>11601</v>
       </c>
-      <c r="K161" s="6"/>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
-    </row>
-    <row r="162" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N161" s="6"/>
+    </row>
+    <row r="162" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>117</v>
       </c>
@@ -9046,11 +9299,14 @@
       <c r="I162" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="K162" s="3"/>
+      <c r="J162" s="2" t="s">
+        <v>875</v>
+      </c>
       <c r="L162" s="3"/>
       <c r="M162" s="3"/>
-    </row>
-    <row r="163" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N162" s="3"/>
+    </row>
+    <row r="163" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>117</v>
       </c>
@@ -9078,11 +9334,11 @@
       <c r="I163" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="K163" s="3"/>
       <c r="L163" s="3"/>
       <c r="M163" s="3"/>
-    </row>
-    <row r="164" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N163" s="3"/>
+    </row>
+    <row r="164" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>117</v>
       </c>
@@ -9110,11 +9366,11 @@
       <c r="I164" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="K164" s="3"/>
       <c r="L164" s="3"/>
       <c r="M164" s="3"/>
-    </row>
-    <row r="165" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N164" s="3"/>
+    </row>
+    <row r="165" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>118</v>
       </c>
@@ -9142,14 +9398,14 @@
       <c r="I165" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="J165" s="2" t="s">
+      <c r="K165" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K165" s="3"/>
       <c r="L165" s="3"/>
       <c r="M165" s="3"/>
-    </row>
-    <row r="166" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N165" s="3"/>
+    </row>
+    <row r="166" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>118</v>
       </c>
@@ -9177,14 +9433,14 @@
       <c r="I166" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="J166" s="2" t="s">
+      <c r="K166" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K166" s="3"/>
       <c r="L166" s="3"/>
       <c r="M166" s="3"/>
-    </row>
-    <row r="167" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N166" s="3"/>
+    </row>
+    <row r="167" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>118</v>
       </c>
@@ -9212,14 +9468,14 @@
       <c r="I167" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="J167" s="2" t="s">
+      <c r="K167" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K167" s="3"/>
       <c r="L167" s="3"/>
       <c r="M167" s="3"/>
-    </row>
-    <row r="168" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N167" s="3"/>
+    </row>
+    <row r="168" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>119</v>
       </c>
@@ -9247,14 +9503,14 @@
       <c r="I168" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="J168" s="2" t="s">
+      <c r="K168" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K168" s="3"/>
       <c r="L168" s="3"/>
       <c r="M168" s="3"/>
-    </row>
-    <row r="169" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N168" s="3"/>
+    </row>
+    <row r="169" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>119</v>
       </c>
@@ -9282,14 +9538,14 @@
       <c r="I169" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="J169" s="2" t="s">
+      <c r="K169" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K169" s="3"/>
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
-    </row>
-    <row r="170" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N169" s="3"/>
+    </row>
+    <row r="170" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>120</v>
       </c>
@@ -9317,11 +9573,11 @@
       <c r="I170" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="K170" s="3"/>
       <c r="L170" s="3"/>
       <c r="M170" s="3"/>
-    </row>
-    <row r="171" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N170" s="3"/>
+    </row>
+    <row r="171" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>120</v>
       </c>
@@ -9349,11 +9605,11 @@
       <c r="I171" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="K171" s="3"/>
       <c r="L171" s="3"/>
       <c r="M171" s="3"/>
-    </row>
-    <row r="172" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N171" s="3"/>
+    </row>
+    <row r="172" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>120</v>
       </c>
@@ -9381,11 +9637,11 @@
       <c r="I172" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="K172" s="3"/>
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
-    </row>
-    <row r="173" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N172" s="3"/>
+    </row>
+    <row r="173" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>120</v>
       </c>
@@ -9413,11 +9669,11 @@
       <c r="I173" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="K173" s="3"/>
       <c r="L173" s="3"/>
       <c r="M173" s="3"/>
-    </row>
-    <row r="174" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N173" s="3"/>
+    </row>
+    <row r="174" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>120</v>
       </c>
@@ -9445,11 +9701,11 @@
       <c r="I174" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="K174" s="3"/>
       <c r="L174" s="3"/>
       <c r="M174" s="3"/>
-    </row>
-    <row r="175" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N174" s="3"/>
+    </row>
+    <row r="175" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>121</v>
       </c>
@@ -9477,11 +9733,11 @@
       <c r="I175" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="K175" s="3"/>
       <c r="L175" s="3"/>
       <c r="M175" s="3"/>
-    </row>
-    <row r="176" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N175" s="3"/>
+    </row>
+    <row r="176" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>122</v>
       </c>
@@ -9509,11 +9765,11 @@
       <c r="I176" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="K176" s="3"/>
       <c r="L176" s="3"/>
       <c r="M176" s="3"/>
-    </row>
-    <row r="177" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N176" s="3"/>
+    </row>
+    <row r="177" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>122</v>
       </c>
@@ -9542,13 +9798,16 @@
         <v>659</v>
       </c>
       <c r="J177" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K177" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K177" s="3"/>
       <c r="L177" s="3"/>
       <c r="M177" s="3"/>
-    </row>
-    <row r="178" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N177" s="3"/>
+    </row>
+    <row r="178" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>123</v>
       </c>
@@ -9576,11 +9835,11 @@
       <c r="I178" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="K178" s="3"/>
       <c r="L178" s="3"/>
       <c r="M178" s="3"/>
-    </row>
-    <row r="179" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N178" s="3"/>
+    </row>
+    <row r="179" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>123</v>
       </c>
@@ -9608,11 +9867,11 @@
       <c r="I179" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="K179" s="3"/>
       <c r="L179" s="3"/>
       <c r="M179" s="3"/>
-    </row>
-    <row r="180" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N179" s="3"/>
+    </row>
+    <row r="180" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>123</v>
       </c>
@@ -9640,11 +9899,11 @@
       <c r="I180" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="K180" s="3"/>
       <c r="L180" s="3"/>
       <c r="M180" s="3"/>
-    </row>
-    <row r="181" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N180" s="3"/>
+    </row>
+    <row r="181" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>123</v>
       </c>
@@ -9673,13 +9932,16 @@
         <v>659</v>
       </c>
       <c r="J181" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K181" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K181" s="3"/>
       <c r="L181" s="3"/>
       <c r="M181" s="3"/>
-    </row>
-    <row r="182" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N181" s="3"/>
+    </row>
+    <row r="182" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>123</v>
       </c>
@@ -9707,11 +9969,11 @@
       <c r="I182" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="K182" s="3"/>
       <c r="L182" s="3"/>
       <c r="M182" s="3"/>
-    </row>
-    <row r="183" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N182" s="3"/>
+    </row>
+    <row r="183" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>123</v>
       </c>
@@ -9739,11 +10001,11 @@
       <c r="I183" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="K183" s="3"/>
       <c r="L183" s="3"/>
       <c r="M183" s="3"/>
-    </row>
-    <row r="184" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N183" s="3"/>
+    </row>
+    <row r="184" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>123</v>
       </c>
@@ -9771,11 +10033,11 @@
       <c r="I184" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="K184" s="3"/>
       <c r="L184" s="3"/>
       <c r="M184" s="3"/>
-    </row>
-    <row r="185" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N184" s="3"/>
+    </row>
+    <row r="185" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>124</v>
       </c>
@@ -9785,11 +10047,11 @@
       <c r="C185" s="1">
         <v>12401</v>
       </c>
-      <c r="K185" s="6"/>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
-    </row>
-    <row r="186" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N185" s="6"/>
+    </row>
+    <row r="186" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>125</v>
       </c>
@@ -9817,11 +10079,11 @@
       <c r="I186" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="K186" s="3"/>
       <c r="L186" s="3"/>
       <c r="M186" s="3"/>
-    </row>
-    <row r="187" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N186" s="3"/>
+    </row>
+    <row r="187" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>125</v>
       </c>
@@ -9849,11 +10111,11 @@
       <c r="I187" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="K187" s="3"/>
       <c r="L187" s="3"/>
       <c r="M187" s="3"/>
-    </row>
-    <row r="188" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N187" s="3"/>
+    </row>
+    <row r="188" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>125</v>
       </c>
@@ -9881,11 +10143,11 @@
       <c r="I188" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="K188" s="3"/>
       <c r="L188" s="3"/>
       <c r="M188" s="3"/>
-    </row>
-    <row r="189" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N188" s="3"/>
+    </row>
+    <row r="189" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>125</v>
       </c>
@@ -9914,13 +10176,16 @@
         <v>659</v>
       </c>
       <c r="J189" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K189" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K189" s="3"/>
       <c r="L189" s="3"/>
       <c r="M189" s="3"/>
-    </row>
-    <row r="190" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N189" s="3"/>
+    </row>
+    <row r="190" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>125</v>
       </c>
@@ -9949,13 +10214,16 @@
         <v>659</v>
       </c>
       <c r="J190" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K190" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K190" s="3"/>
       <c r="L190" s="3"/>
       <c r="M190" s="3"/>
-    </row>
-    <row r="191" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N190" s="3"/>
+    </row>
+    <row r="191" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>126</v>
       </c>
@@ -9983,11 +10251,11 @@
       <c r="I191" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="K191" s="3"/>
       <c r="L191" s="3"/>
       <c r="M191" s="3"/>
-    </row>
-    <row r="192" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N191" s="3"/>
+    </row>
+    <row r="192" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>126</v>
       </c>
@@ -10015,11 +10283,11 @@
       <c r="I192" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="K192" s="3"/>
       <c r="L192" s="3"/>
       <c r="M192" s="3"/>
-    </row>
-    <row r="193" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N192" s="3"/>
+    </row>
+    <row r="193" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>127</v>
       </c>
@@ -10047,11 +10315,11 @@
       <c r="I193" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="K193" s="3"/>
       <c r="L193" s="3"/>
       <c r="M193" s="3"/>
-    </row>
-    <row r="194" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N193" s="3"/>
+    </row>
+    <row r="194" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>127</v>
       </c>
@@ -10079,11 +10347,11 @@
       <c r="I194" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="K194" s="3"/>
       <c r="L194" s="3"/>
       <c r="M194" s="3"/>
-    </row>
-    <row r="195" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N194" s="3"/>
+    </row>
+    <row r="195" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>128</v>
       </c>
@@ -10111,11 +10379,11 @@
       <c r="I195" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="K195" s="3"/>
       <c r="L195" s="3"/>
       <c r="M195" s="3"/>
-    </row>
-    <row r="196" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N195" s="3"/>
+    </row>
+    <row r="196" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>129</v>
       </c>
@@ -10143,11 +10411,11 @@
       <c r="I196" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="K196" s="3"/>
       <c r="L196" s="3"/>
       <c r="M196" s="3"/>
-    </row>
-    <row r="197" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N196" s="3"/>
+    </row>
+    <row r="197" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>130</v>
       </c>
@@ -10175,11 +10443,11 @@
       <c r="I197" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="K197" s="3"/>
       <c r="L197" s="3"/>
       <c r="M197" s="3"/>
-    </row>
-    <row r="198" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N197" s="3"/>
+    </row>
+    <row r="198" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>130</v>
       </c>
@@ -10207,11 +10475,11 @@
       <c r="I198" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="K198" s="3"/>
       <c r="L198" s="3"/>
       <c r="M198" s="3"/>
-    </row>
-    <row r="199" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N198" s="3"/>
+    </row>
+    <row r="199" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>131</v>
       </c>
@@ -10239,11 +10507,11 @@
       <c r="I199" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="K199" s="3"/>
       <c r="L199" s="3"/>
       <c r="M199" s="3"/>
-    </row>
-    <row r="200" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N199" s="3"/>
+    </row>
+    <row r="200" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>131</v>
       </c>
@@ -10271,11 +10539,11 @@
       <c r="I200" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="K200" s="3"/>
       <c r="L200" s="3"/>
       <c r="M200" s="3"/>
-    </row>
-    <row r="201" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N200" s="3"/>
+    </row>
+    <row r="201" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>131</v>
       </c>
@@ -10303,11 +10571,11 @@
       <c r="I201" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="K201" s="3"/>
       <c r="L201" s="3"/>
       <c r="M201" s="3"/>
-    </row>
-    <row r="202" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N201" s="3"/>
+    </row>
+    <row r="202" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>131</v>
       </c>
@@ -10335,11 +10603,11 @@
       <c r="I202" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="K202" s="3"/>
       <c r="L202" s="3"/>
       <c r="M202" s="3"/>
-    </row>
-    <row r="203" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N202" s="3"/>
+    </row>
+    <row r="203" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>131</v>
       </c>
@@ -10367,11 +10635,11 @@
       <c r="I203" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="K203" s="3"/>
       <c r="L203" s="3"/>
       <c r="M203" s="3"/>
-    </row>
-    <row r="204" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N203" s="3"/>
+    </row>
+    <row r="204" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>132</v>
       </c>
@@ -10399,11 +10667,11 @@
       <c r="I204" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="K204" s="3"/>
       <c r="L204" s="3"/>
       <c r="M204" s="3"/>
-    </row>
-    <row r="205" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N204" s="3"/>
+    </row>
+    <row r="205" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>132</v>
       </c>
@@ -10431,11 +10699,11 @@
       <c r="I205" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="K205" s="3"/>
       <c r="L205" s="3"/>
       <c r="M205" s="3"/>
-    </row>
-    <row r="206" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N205" s="3"/>
+    </row>
+    <row r="206" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>132</v>
       </c>
@@ -10463,11 +10731,11 @@
       <c r="I206" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="K206" s="3"/>
       <c r="L206" s="3"/>
       <c r="M206" s="3"/>
-    </row>
-    <row r="207" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N206" s="3"/>
+    </row>
+    <row r="207" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>132</v>
       </c>
@@ -10495,11 +10763,11 @@
       <c r="I207" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="K207" s="3"/>
       <c r="L207" s="3"/>
       <c r="M207" s="3"/>
-    </row>
-    <row r="208" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N207" s="3"/>
+    </row>
+    <row r="208" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>133</v>
       </c>
@@ -10528,13 +10796,16 @@
         <v>659</v>
       </c>
       <c r="J208" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="K208" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K208" s="3"/>
       <c r="L208" s="3"/>
       <c r="M208" s="3"/>
-    </row>
-    <row r="209" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N208" s="3"/>
+    </row>
+    <row r="209" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>133</v>
       </c>
@@ -10562,11 +10833,11 @@
       <c r="I209" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="K209" s="3"/>
       <c r="L209" s="3"/>
       <c r="M209" s="3"/>
-    </row>
-    <row r="210" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N209" s="3"/>
+    </row>
+    <row r="210" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>133</v>
       </c>
@@ -10594,11 +10865,11 @@
       <c r="I210" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="K210" s="3"/>
       <c r="L210" s="3"/>
       <c r="M210" s="3"/>
-    </row>
-    <row r="211" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N210" s="3"/>
+    </row>
+    <row r="211" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>133</v>
       </c>
@@ -10626,11 +10897,11 @@
       <c r="I211" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="K211" s="3"/>
       <c r="L211" s="3"/>
       <c r="M211" s="3"/>
-    </row>
-    <row r="212" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N211" s="3"/>
+    </row>
+    <row r="212" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>133</v>
       </c>
@@ -10658,11 +10929,11 @@
       <c r="I212" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="K212" s="3"/>
       <c r="L212" s="3"/>
       <c r="M212" s="3"/>
-    </row>
-    <row r="213" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N212" s="3"/>
+    </row>
+    <row r="213" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>133</v>
       </c>
@@ -10690,11 +10961,11 @@
       <c r="I213" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="K213" s="3"/>
       <c r="L213" s="3"/>
       <c r="M213" s="3"/>
-    </row>
-    <row r="214" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N213" s="3"/>
+    </row>
+    <row r="214" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>133</v>
       </c>
@@ -10722,11 +10993,11 @@
       <c r="I214" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="K214" s="3"/>
       <c r="L214" s="3"/>
       <c r="M214" s="3"/>
-    </row>
-    <row r="215" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N214" s="3"/>
+    </row>
+    <row r="215" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>133</v>
       </c>
@@ -10754,11 +11025,11 @@
       <c r="I215" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="K215" s="3"/>
       <c r="L215" s="3"/>
       <c r="M215" s="3"/>
-    </row>
-    <row r="216" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N215" s="3"/>
+    </row>
+    <row r="216" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>133</v>
       </c>
@@ -10786,11 +11057,11 @@
       <c r="I216" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="K216" s="3"/>
       <c r="L216" s="3"/>
       <c r="M216" s="3"/>
-    </row>
-    <row r="217" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N216" s="3"/>
+    </row>
+    <row r="217" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>134</v>
       </c>
@@ -10818,11 +11089,11 @@
       <c r="I217" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="K217" s="3"/>
       <c r="L217" s="3"/>
       <c r="M217" s="3"/>
-    </row>
-    <row r="218" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N217" s="3"/>
+    </row>
+    <row r="218" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>134</v>
       </c>
@@ -10850,11 +11121,11 @@
       <c r="I218" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="K218" s="3"/>
       <c r="L218" s="3"/>
       <c r="M218" s="3"/>
-    </row>
-    <row r="219" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N218" s="3"/>
+    </row>
+    <row r="219" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>134</v>
       </c>
@@ -10882,11 +11153,11 @@
       <c r="I219" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="K219" s="3"/>
       <c r="L219" s="3"/>
       <c r="M219" s="3"/>
-    </row>
-    <row r="220" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N219" s="3"/>
+    </row>
+    <row r="220" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>134</v>
       </c>
@@ -10914,11 +11185,11 @@
       <c r="I220" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="K220" s="3"/>
       <c r="L220" s="3"/>
       <c r="M220" s="3"/>
-    </row>
-    <row r="221" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N220" s="3"/>
+    </row>
+    <row r="221" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>134</v>
       </c>
@@ -10946,11 +11217,11 @@
       <c r="I221" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="K221" s="3"/>
       <c r="L221" s="3"/>
       <c r="M221" s="3"/>
-    </row>
-    <row r="222" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N221" s="3"/>
+    </row>
+    <row r="222" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>134</v>
       </c>
@@ -10978,11 +11249,11 @@
       <c r="I222" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="K222" s="3"/>
       <c r="L222" s="3"/>
       <c r="M222" s="3"/>
-    </row>
-    <row r="223" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N222" s="3"/>
+    </row>
+    <row r="223" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>134</v>
       </c>
@@ -11010,11 +11281,11 @@
       <c r="I223" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="K223" s="3"/>
       <c r="L223" s="3"/>
       <c r="M223" s="3"/>
-    </row>
-    <row r="224" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N223" s="3"/>
+    </row>
+    <row r="224" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>134</v>
       </c>
@@ -11042,11 +11313,11 @@
       <c r="I224" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="K224" s="3"/>
       <c r="L224" s="3"/>
       <c r="M224" s="3"/>
-    </row>
-    <row r="225" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N224" s="3"/>
+    </row>
+    <row r="225" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>134</v>
       </c>
@@ -11074,11 +11345,11 @@
       <c r="I225" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="K225" s="3"/>
       <c r="L225" s="3"/>
       <c r="M225" s="3"/>
-    </row>
-    <row r="226" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N225" s="3"/>
+    </row>
+    <row r="226" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>134</v>
       </c>
@@ -11106,11 +11377,11 @@
       <c r="I226" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="K226" s="3"/>
       <c r="L226" s="3"/>
       <c r="M226" s="3"/>
-    </row>
-    <row r="227" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N226" s="3"/>
+    </row>
+    <row r="227" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>134</v>
       </c>
@@ -11138,11 +11409,11 @@
       <c r="I227" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="K227" s="3"/>
       <c r="L227" s="3"/>
       <c r="M227" s="3"/>
-    </row>
-    <row r="228" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N227" s="3"/>
+    </row>
+    <row r="228" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>134</v>
       </c>
@@ -11170,11 +11441,11 @@
       <c r="I228" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="K228" s="3"/>
       <c r="L228" s="3"/>
       <c r="M228" s="3"/>
-    </row>
-    <row r="229" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N228" s="3"/>
+    </row>
+    <row r="229" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>135</v>
       </c>
@@ -11202,11 +11473,11 @@
       <c r="I229" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="K229" s="3"/>
       <c r="L229" s="3"/>
       <c r="M229" s="3"/>
-    </row>
-    <row r="230" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N229" s="3"/>
+    </row>
+    <row r="230" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>135</v>
       </c>
@@ -11234,11 +11505,11 @@
       <c r="I230" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="K230" s="3"/>
       <c r="L230" s="3"/>
       <c r="M230" s="3"/>
-    </row>
-    <row r="231" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N230" s="3"/>
+    </row>
+    <row r="231" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>135</v>
       </c>
@@ -11266,11 +11537,11 @@
       <c r="I231" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="K231" s="3"/>
       <c r="L231" s="3"/>
       <c r="M231" s="3"/>
-    </row>
-    <row r="232" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N231" s="3"/>
+    </row>
+    <row r="232" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>135</v>
       </c>
@@ -11298,11 +11569,11 @@
       <c r="I232" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="K232" s="3"/>
       <c r="L232" s="3"/>
       <c r="M232" s="3"/>
-    </row>
-    <row r="233" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N232" s="3"/>
+    </row>
+    <row r="233" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>135</v>
       </c>
@@ -11330,11 +11601,11 @@
       <c r="I233" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="K233" s="3"/>
       <c r="L233" s="3"/>
       <c r="M233" s="3"/>
-    </row>
-    <row r="234" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N233" s="3"/>
+    </row>
+    <row r="234" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>135</v>
       </c>
@@ -11362,11 +11633,11 @@
       <c r="I234" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="K234" s="3"/>
       <c r="L234" s="3"/>
       <c r="M234" s="3"/>
-    </row>
-    <row r="235" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N234" s="3"/>
+    </row>
+    <row r="235" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>135</v>
       </c>
@@ -11394,11 +11665,11 @@
       <c r="I235" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K235" s="3"/>
       <c r="L235" s="3"/>
       <c r="M235" s="3"/>
-    </row>
-    <row r="236" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N235" s="3"/>
+    </row>
+    <row r="236" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>136</v>
       </c>
@@ -11426,11 +11697,11 @@
       <c r="I236" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="K236" s="3"/>
       <c r="L236" s="3"/>
       <c r="M236" s="3"/>
-    </row>
-    <row r="237" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N236" s="3"/>
+    </row>
+    <row r="237" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>136</v>
       </c>
@@ -11458,11 +11729,11 @@
       <c r="I237" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="K237" s="3"/>
       <c r="L237" s="3"/>
       <c r="M237" s="3"/>
-    </row>
-    <row r="238" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N237" s="3"/>
+    </row>
+    <row r="238" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>137</v>
       </c>
@@ -11490,11 +11761,11 @@
       <c r="I238" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K238" s="3"/>
       <c r="L238" s="3"/>
       <c r="M238" s="3"/>
-    </row>
-    <row r="239" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N238" s="3"/>
+    </row>
+    <row r="239" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>137</v>
       </c>
@@ -11522,11 +11793,11 @@
       <c r="I239" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K239" s="3"/>
       <c r="L239" s="3"/>
       <c r="M239" s="3"/>
-    </row>
-    <row r="240" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N239" s="3"/>
+    </row>
+    <row r="240" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>137</v>
       </c>
@@ -11554,11 +11825,11 @@
       <c r="I240" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K240" s="3"/>
       <c r="L240" s="3"/>
       <c r="M240" s="3"/>
-    </row>
-    <row r="241" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N240" s="3"/>
+    </row>
+    <row r="241" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>137</v>
       </c>
@@ -11586,11 +11857,11 @@
       <c r="I241" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K241" s="3"/>
       <c r="L241" s="3"/>
       <c r="M241" s="3"/>
-    </row>
-    <row r="242" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N241" s="3"/>
+    </row>
+    <row r="242" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>137</v>
       </c>
@@ -11618,11 +11889,11 @@
       <c r="I242" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="K242" s="3"/>
       <c r="L242" s="3"/>
       <c r="M242" s="3"/>
-    </row>
-    <row r="243" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N242" s="3"/>
+    </row>
+    <row r="243" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>137</v>
       </c>
@@ -11650,11 +11921,11 @@
       <c r="I243" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="K243" s="3"/>
       <c r="L243" s="3"/>
       <c r="M243" s="3"/>
-    </row>
-    <row r="244" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N243" s="3"/>
+    </row>
+    <row r="244" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>137</v>
       </c>
@@ -11682,17 +11953,17 @@
       <c r="I244" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="K244" s="3" t="s">
+      <c r="L244" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L244" s="3" t="s">
+      <c r="M244" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="M244" s="3" t="s">
+      <c r="N244" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="245" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>137</v>
       </c>
@@ -11720,17 +11991,17 @@
       <c r="I245" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="K245" s="3" t="s">
+      <c r="L245" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L245" s="3" t="s">
+      <c r="M245" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="M245" s="3" t="s">
+      <c r="N245" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="246" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>137</v>
       </c>
@@ -11758,17 +12029,17 @@
       <c r="I246" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="K246" s="3" t="s">
+      <c r="L246" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L246" s="3" t="s">
+      <c r="M246" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="M246" s="3" t="s">
+      <c r="N246" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="247" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>138</v>
       </c>
@@ -11796,11 +12067,11 @@
       <c r="I247" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="K247" s="3"/>
       <c r="L247" s="3"/>
       <c r="M247" s="3"/>
-    </row>
-    <row r="248" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N247" s="3"/>
+    </row>
+    <row r="248" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>138</v>
       </c>
@@ -11828,11 +12099,11 @@
       <c r="I248" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="K248" s="3"/>
       <c r="L248" s="3"/>
       <c r="M248" s="3"/>
-    </row>
-    <row r="249" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N248" s="3"/>
+    </row>
+    <row r="249" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>138</v>
       </c>
@@ -11860,11 +12131,11 @@
       <c r="I249" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="K249" s="3"/>
       <c r="L249" s="3"/>
       <c r="M249" s="3"/>
-    </row>
-    <row r="250" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N249" s="3"/>
+    </row>
+    <row r="250" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>138</v>
       </c>
@@ -11892,17 +12163,17 @@
       <c r="I250" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="K250" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L250" s="3" t="s">
         <v>91</v>
       </c>
       <c r="M250" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="251" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N250" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>139</v>
       </c>
@@ -11930,11 +12201,11 @@
       <c r="I251" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="K251" s="3"/>
       <c r="L251" s="3"/>
       <c r="M251" s="3"/>
-    </row>
-    <row r="252" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N251" s="3"/>
+    </row>
+    <row r="252" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>140</v>
       </c>
@@ -11962,11 +12233,11 @@
       <c r="I252" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K252" s="3"/>
       <c r="L252" s="3"/>
       <c r="M252" s="3"/>
-    </row>
-    <row r="253" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N252" s="3"/>
+    </row>
+    <row r="253" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>140</v>
       </c>
@@ -11994,11 +12265,11 @@
       <c r="I253" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K253" s="3"/>
       <c r="L253" s="3"/>
       <c r="M253" s="3"/>
-    </row>
-    <row r="254" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N253" s="3"/>
+    </row>
+    <row r="254" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>140</v>
       </c>
@@ -12026,11 +12297,11 @@
       <c r="I254" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K254" s="3"/>
       <c r="L254" s="3"/>
       <c r="M254" s="3"/>
-    </row>
-    <row r="255" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N254" s="3"/>
+    </row>
+    <row r="255" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>140</v>
       </c>
@@ -12058,11 +12329,11 @@
       <c r="I255" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K255" s="3"/>
       <c r="L255" s="3"/>
       <c r="M255" s="3"/>
-    </row>
-    <row r="256" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N255" s="3"/>
+    </row>
+    <row r="256" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>140</v>
       </c>
@@ -12090,11 +12361,11 @@
       <c r="I256" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="K256" s="3"/>
       <c r="L256" s="3"/>
       <c r="M256" s="3"/>
-    </row>
-    <row r="257" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N256" s="3"/>
+    </row>
+    <row r="257" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>140</v>
       </c>
@@ -12122,17 +12393,17 @@
       <c r="I257" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K257" s="3" t="s">
+      <c r="L257" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L257" s="3">
+      <c r="M257" s="3">
         <v>0</v>
       </c>
-      <c r="M257" s="3" t="s">
+      <c r="N257" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="258" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>140</v>
       </c>
@@ -12160,17 +12431,17 @@
       <c r="I258" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K258" s="3" t="s">
+      <c r="L258" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L258" s="3">
+      <c r="M258" s="3">
         <v>25</v>
       </c>
-      <c r="M258" s="3" t="s">
+      <c r="N258" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="259" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>140</v>
       </c>
@@ -12198,17 +12469,17 @@
       <c r="I259" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K259" s="3" t="s">
+      <c r="L259" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L259" s="3">
+      <c r="M259" s="3">
         <v>45</v>
       </c>
-      <c r="M259" s="3" t="s">
+      <c r="N259" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="260" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>140</v>
       </c>
@@ -12236,17 +12507,17 @@
       <c r="I260" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K260" s="3" t="s">
+      <c r="L260" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L260" s="3">
+      <c r="M260" s="3">
         <v>70</v>
       </c>
-      <c r="M260" s="3" t="s">
+      <c r="N260" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="261" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>140</v>
       </c>
@@ -12274,17 +12545,17 @@
       <c r="I261" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K261" s="3" t="s">
+      <c r="L261" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="L261" s="3">
+      <c r="M261" s="3">
         <v>0</v>
       </c>
-      <c r="M261" s="3" t="s">
+      <c r="N261" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="262" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>140</v>
       </c>
@@ -12312,17 +12583,17 @@
       <c r="I262" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K262" s="3" t="s">
+      <c r="L262" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="L262" s="3">
+      <c r="M262" s="3">
         <v>15</v>
       </c>
-      <c r="M262" s="3" t="s">
+      <c r="N262" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="263" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>140</v>
       </c>
@@ -12350,17 +12621,17 @@
       <c r="I263" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K263" s="3" t="s">
+      <c r="L263" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="L263" s="3">
+      <c r="M263" s="3">
         <v>30</v>
       </c>
-      <c r="M263" s="3" t="s">
+      <c r="N263" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="264" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>140</v>
       </c>
@@ -12388,17 +12659,17 @@
       <c r="I264" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K264" s="3" t="s">
+      <c r="L264" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="L264" s="3">
+      <c r="M264" s="3">
         <v>50</v>
       </c>
-      <c r="M264" s="3" t="s">
+      <c r="N264" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="265" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>141</v>
       </c>
@@ -12408,11 +12679,11 @@
       <c r="C265" s="1">
         <v>14101</v>
       </c>
-      <c r="K265" s="6"/>
       <c r="L265" s="6"/>
       <c r="M265" s="6"/>
-    </row>
-    <row r="266" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N265" s="6"/>
+    </row>
+    <row r="266" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>142</v>
       </c>
@@ -12440,11 +12711,11 @@
       <c r="I266" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="K266" s="3"/>
       <c r="L266" s="3"/>
       <c r="M266" s="3"/>
-    </row>
-    <row r="267" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N266" s="3"/>
+    </row>
+    <row r="267" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>142</v>
       </c>
@@ -12472,11 +12743,11 @@
       <c r="I267" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="K267" s="3"/>
       <c r="L267" s="3"/>
       <c r="M267" s="3"/>
-    </row>
-    <row r="268" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N267" s="3"/>
+    </row>
+    <row r="268" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>142</v>
       </c>
@@ -12504,11 +12775,11 @@
       <c r="I268" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="K268" s="3"/>
       <c r="L268" s="3"/>
       <c r="M268" s="3"/>
-    </row>
-    <row r="269" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N268" s="3"/>
+    </row>
+    <row r="269" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>142</v>
       </c>
@@ -12536,11 +12807,11 @@
       <c r="I269" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="K269" s="3"/>
       <c r="L269" s="3"/>
       <c r="M269" s="3"/>
-    </row>
-    <row r="270" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N269" s="3"/>
+    </row>
+    <row r="270" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>142</v>
       </c>
@@ -12568,11 +12839,11 @@
       <c r="I270" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="K270" s="3"/>
       <c r="L270" s="3"/>
       <c r="M270" s="3"/>
-    </row>
-    <row r="271" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N270" s="3"/>
+    </row>
+    <row r="271" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>142</v>
       </c>
@@ -12600,11 +12871,11 @@
       <c r="I271" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="K271" s="3"/>
       <c r="L271" s="3"/>
       <c r="M271" s="3"/>
-    </row>
-    <row r="272" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N271" s="3"/>
+    </row>
+    <row r="272" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>142</v>
       </c>
@@ -12632,11 +12903,11 @@
       <c r="I272" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="K272" s="3"/>
       <c r="L272" s="3"/>
       <c r="M272" s="3"/>
-    </row>
-    <row r="273" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N272" s="3"/>
+    </row>
+    <row r="273" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>142</v>
       </c>
@@ -12664,11 +12935,11 @@
       <c r="I273" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K273" s="3"/>
       <c r="L273" s="3"/>
       <c r="M273" s="3"/>
-    </row>
-    <row r="274" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N273" s="3"/>
+    </row>
+    <row r="274" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>142</v>
       </c>
@@ -12696,11 +12967,11 @@
       <c r="I274" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K274" s="3"/>
       <c r="L274" s="3"/>
       <c r="M274" s="3"/>
-    </row>
-    <row r="275" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N274" s="3"/>
+    </row>
+    <row r="275" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>142</v>
       </c>
@@ -12728,11 +12999,11 @@
       <c r="I275" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K275" s="3"/>
       <c r="L275" s="3"/>
       <c r="M275" s="3"/>
-    </row>
-    <row r="276" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N275" s="3"/>
+    </row>
+    <row r="276" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>142</v>
       </c>
@@ -12760,11 +13031,11 @@
       <c r="I276" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K276" s="3"/>
       <c r="L276" s="3"/>
       <c r="M276" s="3"/>
-    </row>
-    <row r="277" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N276" s="3"/>
+    </row>
+    <row r="277" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>142</v>
       </c>
@@ -12792,11 +13063,11 @@
       <c r="I277" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K277" s="3"/>
       <c r="L277" s="3"/>
       <c r="M277" s="3"/>
-    </row>
-    <row r="278" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N277" s="3"/>
+    </row>
+    <row r="278" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>142</v>
       </c>
@@ -12824,11 +13095,11 @@
       <c r="I278" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K278" s="3"/>
       <c r="L278" s="3"/>
       <c r="M278" s="3"/>
-    </row>
-    <row r="279" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N278" s="3"/>
+    </row>
+    <row r="279" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>142</v>
       </c>
@@ -12856,11 +13127,11 @@
       <c r="I279" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K279" s="3"/>
       <c r="L279" s="3"/>
       <c r="M279" s="3"/>
-    </row>
-    <row r="280" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N279" s="3"/>
+    </row>
+    <row r="280" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>142</v>
       </c>
@@ -12888,11 +13159,11 @@
       <c r="I280" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K280" s="3"/>
       <c r="L280" s="3"/>
       <c r="M280" s="3"/>
-    </row>
-    <row r="281" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N280" s="3"/>
+    </row>
+    <row r="281" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>142</v>
       </c>
@@ -12920,11 +13191,11 @@
       <c r="I281" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K281" s="3"/>
       <c r="L281" s="3"/>
       <c r="M281" s="3"/>
-    </row>
-    <row r="282" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N281" s="3"/>
+    </row>
+    <row r="282" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>142</v>
       </c>
@@ -12952,11 +13223,11 @@
       <c r="I282" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K282" s="3"/>
       <c r="L282" s="3"/>
       <c r="M282" s="3"/>
-    </row>
-    <row r="283" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N282" s="3"/>
+    </row>
+    <row r="283" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>142</v>
       </c>
@@ -12984,11 +13255,11 @@
       <c r="I283" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K283" s="3"/>
       <c r="L283" s="3"/>
       <c r="M283" s="3"/>
-    </row>
-    <row r="284" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N283" s="3"/>
+    </row>
+    <row r="284" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>142</v>
       </c>
@@ -13016,11 +13287,11 @@
       <c r="I284" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K284" s="3"/>
       <c r="L284" s="3"/>
       <c r="M284" s="3"/>
-    </row>
-    <row r="285" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N284" s="3"/>
+    </row>
+    <row r="285" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>142</v>
       </c>
@@ -13048,11 +13319,11 @@
       <c r="I285" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K285" s="3"/>
       <c r="L285" s="3"/>
       <c r="M285" s="3"/>
-    </row>
-    <row r="286" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N285" s="3"/>
+    </row>
+    <row r="286" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>142</v>
       </c>
@@ -13080,11 +13351,11 @@
       <c r="I286" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K286" s="3"/>
       <c r="L286" s="3"/>
       <c r="M286" s="3"/>
-    </row>
-    <row r="287" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N286" s="3"/>
+    </row>
+    <row r="287" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>142</v>
       </c>
@@ -13112,11 +13383,11 @@
       <c r="I287" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K287" s="3"/>
       <c r="L287" s="3"/>
       <c r="M287" s="3"/>
-    </row>
-    <row r="288" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N287" s="3"/>
+    </row>
+    <row r="288" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>142</v>
       </c>
@@ -13144,11 +13415,11 @@
       <c r="I288" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="K288" s="3"/>
       <c r="L288" s="3"/>
       <c r="M288" s="3"/>
-    </row>
-    <row r="289" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N288" s="3"/>
+    </row>
+    <row r="289" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>142</v>
       </c>
@@ -13176,11 +13447,11 @@
       <c r="I289" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="K289" s="3"/>
       <c r="L289" s="3"/>
       <c r="M289" s="3"/>
-    </row>
-    <row r="290" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N289" s="3"/>
+    </row>
+    <row r="290" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>142</v>
       </c>
@@ -13208,11 +13479,11 @@
       <c r="I290" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="K290" s="3"/>
       <c r="L290" s="3"/>
       <c r="M290" s="3"/>
-    </row>
-    <row r="291" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N290" s="3"/>
+    </row>
+    <row r="291" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>142</v>
       </c>
@@ -13240,11 +13511,11 @@
       <c r="I291" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="K291" s="3"/>
       <c r="L291" s="3"/>
       <c r="M291" s="3"/>
-    </row>
-    <row r="292" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N291" s="3"/>
+    </row>
+    <row r="292" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>142</v>
       </c>
@@ -13272,11 +13543,11 @@
       <c r="I292" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="K292" s="3"/>
       <c r="L292" s="3"/>
       <c r="M292" s="3"/>
-    </row>
-    <row r="293" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N292" s="3"/>
+    </row>
+    <row r="293" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>142</v>
       </c>
@@ -13304,11 +13575,11 @@
       <c r="I293" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="K293" s="3"/>
       <c r="L293" s="3"/>
       <c r="M293" s="3"/>
-    </row>
-    <row r="294" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N293" s="3"/>
+    </row>
+    <row r="294" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>142</v>
       </c>
@@ -13336,11 +13607,11 @@
       <c r="I294" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="K294" s="3"/>
       <c r="L294" s="3"/>
       <c r="M294" s="3"/>
-    </row>
-    <row r="295" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N294" s="3"/>
+    </row>
+    <row r="295" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>143</v>
       </c>
@@ -13368,11 +13639,11 @@
       <c r="I295" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="K295" s="3"/>
       <c r="L295" s="3"/>
       <c r="M295" s="3"/>
-    </row>
-    <row r="296" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N295" s="3"/>
+    </row>
+    <row r="296" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>143</v>
       </c>
@@ -13400,11 +13671,11 @@
       <c r="I296" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="K296" s="3"/>
       <c r="L296" s="3"/>
       <c r="M296" s="3"/>
-    </row>
-    <row r="297" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N296" s="3"/>
+    </row>
+    <row r="297" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>143</v>
       </c>
@@ -13432,11 +13703,11 @@
       <c r="I297" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="K297" s="3"/>
       <c r="L297" s="3"/>
       <c r="M297" s="3"/>
-    </row>
-    <row r="298" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N297" s="3"/>
+    </row>
+    <row r="298" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>143</v>
       </c>
@@ -13464,11 +13735,11 @@
       <c r="I298" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="K298" s="3"/>
       <c r="L298" s="3"/>
       <c r="M298" s="3"/>
-    </row>
-    <row r="299" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N298" s="3"/>
+    </row>
+    <row r="299" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>143</v>
       </c>
@@ -13496,11 +13767,11 @@
       <c r="I299" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="K299" s="3"/>
       <c r="L299" s="3"/>
       <c r="M299" s="3"/>
-    </row>
-    <row r="300" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N299" s="3"/>
+    </row>
+    <row r="300" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>144</v>
       </c>
@@ -13528,11 +13799,11 @@
       <c r="I300" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="K300" s="3"/>
       <c r="L300" s="3"/>
       <c r="M300" s="3"/>
-    </row>
-    <row r="301" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N300" s="3"/>
+    </row>
+    <row r="301" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>144</v>
       </c>
@@ -13560,14 +13831,14 @@
       <c r="I301" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J301" s="2" t="s">
+      <c r="K301" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K301" s="3"/>
       <c r="L301" s="3"/>
       <c r="M301" s="3"/>
-    </row>
-    <row r="302" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N301" s="3"/>
+    </row>
+    <row r="302" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>144</v>
       </c>
@@ -13595,11 +13866,11 @@
       <c r="I302" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="K302" s="3"/>
       <c r="L302" s="3"/>
       <c r="M302" s="3"/>
-    </row>
-    <row r="303" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N302" s="3"/>
+    </row>
+    <row r="303" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>144</v>
       </c>
@@ -13627,11 +13898,11 @@
       <c r="I303" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="K303" s="3"/>
       <c r="L303" s="3"/>
       <c r="M303" s="3"/>
-    </row>
-    <row r="304" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N303" s="3"/>
+    </row>
+    <row r="304" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>144</v>
       </c>
@@ -13659,11 +13930,11 @@
       <c r="I304" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="K304" s="3"/>
       <c r="L304" s="3"/>
       <c r="M304" s="3"/>
-    </row>
-    <row r="305" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N304" s="3"/>
+    </row>
+    <row r="305" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>144</v>
       </c>
@@ -13691,11 +13962,11 @@
       <c r="I305" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="K305" s="3"/>
       <c r="L305" s="3"/>
       <c r="M305" s="3"/>
-    </row>
-    <row r="306" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N305" s="3"/>
+    </row>
+    <row r="306" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>145</v>
       </c>
@@ -13723,14 +13994,14 @@
       <c r="I306" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="J306" s="2" t="s">
+      <c r="K306" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="K306" s="3"/>
       <c r="L306" s="3"/>
       <c r="M306" s="3"/>
-    </row>
-    <row r="307" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N306" s="3"/>
+    </row>
+    <row r="307" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>145</v>
       </c>
@@ -13758,11 +14029,11 @@
       <c r="I307" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="K307" s="3"/>
       <c r="L307" s="3"/>
       <c r="M307" s="3"/>
-    </row>
-    <row r="308" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N307" s="3"/>
+    </row>
+    <row r="308" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>145</v>
       </c>
@@ -13790,11 +14061,11 @@
       <c r="I308" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="K308" s="3"/>
       <c r="L308" s="3"/>
       <c r="M308" s="3"/>
-    </row>
-    <row r="309" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N308" s="3"/>
+    </row>
+    <row r="309" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>145</v>
       </c>
@@ -13822,14 +14093,14 @@
       <c r="I309" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="J309" s="2" t="s">
+      <c r="K309" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="K309" s="3"/>
       <c r="L309" s="3"/>
       <c r="M309" s="3"/>
-    </row>
-    <row r="310" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N309" s="3"/>
+    </row>
+    <row r="310" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>145</v>
       </c>
@@ -13857,14 +14128,14 @@
       <c r="I310" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="J310" s="2" t="s">
+      <c r="K310" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="K310" s="3"/>
       <c r="L310" s="3"/>
       <c r="M310" s="3"/>
-    </row>
-    <row r="311" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N310" s="3"/>
+    </row>
+    <row r="311" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>145</v>
       </c>
@@ -13892,14 +14163,14 @@
       <c r="I311" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="J311" s="2" t="s">
+      <c r="K311" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="K311" s="3"/>
       <c r="L311" s="3"/>
       <c r="M311" s="3"/>
-    </row>
-    <row r="312" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N311" s="3"/>
+    </row>
+    <row r="312" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>146</v>
       </c>
@@ -13927,11 +14198,11 @@
       <c r="I312" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="K312" s="3"/>
       <c r="L312" s="3"/>
       <c r="M312" s="3"/>
-    </row>
-    <row r="313" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N312" s="3"/>
+    </row>
+    <row r="313" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>146</v>
       </c>
@@ -13959,11 +14230,11 @@
       <c r="I313" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="K313" s="3"/>
       <c r="L313" s="3"/>
       <c r="M313" s="3"/>
-    </row>
-    <row r="314" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N313" s="3"/>
+    </row>
+    <row r="314" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>146</v>
       </c>
@@ -13991,11 +14262,11 @@
       <c r="I314" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="K314" s="3"/>
       <c r="L314" s="3"/>
       <c r="M314" s="3"/>
-    </row>
-    <row r="315" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N314" s="3"/>
+    </row>
+    <row r="315" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>147</v>
       </c>
@@ -14023,11 +14294,11 @@
       <c r="I315" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K315" s="3"/>
       <c r="L315" s="3"/>
       <c r="M315" s="3"/>
-    </row>
-    <row r="316" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N315" s="3"/>
+    </row>
+    <row r="316" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>147</v>
       </c>
@@ -14055,11 +14326,11 @@
       <c r="I316" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K316" s="3"/>
       <c r="L316" s="3"/>
       <c r="M316" s="3"/>
-    </row>
-    <row r="317" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N316" s="3"/>
+    </row>
+    <row r="317" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>147</v>
       </c>
@@ -14087,11 +14358,11 @@
       <c r="I317" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K317" s="3"/>
       <c r="L317" s="3"/>
       <c r="M317" s="3"/>
-    </row>
-    <row r="318" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N317" s="3"/>
+    </row>
+    <row r="318" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>147</v>
       </c>
@@ -14119,11 +14390,11 @@
       <c r="I318" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K318" s="3"/>
       <c r="L318" s="3"/>
       <c r="M318" s="3"/>
-    </row>
-    <row r="319" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N318" s="3"/>
+    </row>
+    <row r="319" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>148</v>
       </c>
@@ -14151,14 +14422,14 @@
       <c r="I319" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="J319" s="2" t="s">
+      <c r="K319" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K319" s="3"/>
       <c r="L319" s="3"/>
       <c r="M319" s="3"/>
-    </row>
-    <row r="320" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N319" s="3"/>
+    </row>
+    <row r="320" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>148</v>
       </c>
@@ -14186,14 +14457,14 @@
       <c r="I320" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="J320" s="2" t="s">
+      <c r="K320" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K320" s="3"/>
       <c r="L320" s="3"/>
       <c r="M320" s="3"/>
-    </row>
-    <row r="321" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N320" s="3"/>
+    </row>
+    <row r="321" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>148</v>
       </c>
@@ -14221,14 +14492,14 @@
       <c r="I321" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J321" s="2" t="s">
+      <c r="K321" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K321" s="3"/>
       <c r="L321" s="3"/>
       <c r="M321" s="3"/>
-    </row>
-    <row r="322" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N321" s="3"/>
+    </row>
+    <row r="322" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>148</v>
       </c>
@@ -14256,11 +14527,11 @@
       <c r="I322" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="K322" s="3"/>
       <c r="L322" s="3"/>
       <c r="M322" s="3"/>
-    </row>
-    <row r="323" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N322" s="3"/>
+    </row>
+    <row r="323" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>148</v>
       </c>
@@ -14288,11 +14559,11 @@
       <c r="I323" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="K323" s="3"/>
       <c r="L323" s="3"/>
       <c r="M323" s="3"/>
-    </row>
-    <row r="324" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N323" s="3"/>
+    </row>
+    <row r="324" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>148</v>
       </c>
@@ -14320,11 +14591,11 @@
       <c r="I324" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="K324" s="3"/>
       <c r="L324" s="3"/>
       <c r="M324" s="3"/>
-    </row>
-    <row r="325" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N324" s="3"/>
+    </row>
+    <row r="325" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>149</v>
       </c>
@@ -14352,14 +14623,14 @@
       <c r="I325" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="J325" s="2" t="s">
+      <c r="K325" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="K325" s="3"/>
       <c r="L325" s="3"/>
       <c r="M325" s="3"/>
-    </row>
-    <row r="326" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N325" s="3"/>
+    </row>
+    <row r="326" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>149</v>
       </c>
@@ -14387,11 +14658,11 @@
       <c r="I326" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K326" s="3"/>
       <c r="L326" s="3"/>
       <c r="M326" s="3"/>
-    </row>
-    <row r="327" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N326" s="3"/>
+    </row>
+    <row r="327" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>149</v>
       </c>
@@ -14419,11 +14690,11 @@
       <c r="I327" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K327" s="3"/>
       <c r="L327" s="3"/>
       <c r="M327" s="3"/>
-    </row>
-    <row r="328" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N327" s="3"/>
+    </row>
+    <row r="328" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>149</v>
       </c>
@@ -14451,11 +14722,11 @@
       <c r="I328" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K328" s="3"/>
       <c r="L328" s="3"/>
       <c r="M328" s="3"/>
-    </row>
-    <row r="329" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N328" s="3"/>
+    </row>
+    <row r="329" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>149</v>
       </c>
@@ -14483,11 +14754,11 @@
       <c r="I329" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K329" s="3"/>
       <c r="L329" s="3"/>
       <c r="M329" s="3"/>
-    </row>
-    <row r="330" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N329" s="3"/>
+    </row>
+    <row r="330" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>149</v>
       </c>
@@ -14515,11 +14786,11 @@
       <c r="I330" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K330" s="3"/>
       <c r="L330" s="3"/>
       <c r="M330" s="3"/>
-    </row>
-    <row r="331" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N330" s="3"/>
+    </row>
+    <row r="331" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>149</v>
       </c>
@@ -14547,11 +14818,11 @@
       <c r="I331" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K331" s="3"/>
       <c r="L331" s="3"/>
       <c r="M331" s="3"/>
-    </row>
-    <row r="332" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N331" s="3"/>
+    </row>
+    <row r="332" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>149</v>
       </c>
@@ -14579,11 +14850,11 @@
       <c r="I332" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K332" s="3"/>
       <c r="L332" s="3"/>
       <c r="M332" s="3"/>
-    </row>
-    <row r="333" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N332" s="3"/>
+    </row>
+    <row r="333" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>149</v>
       </c>
@@ -14611,11 +14882,11 @@
       <c r="I333" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K333" s="3"/>
       <c r="L333" s="3"/>
       <c r="M333" s="3"/>
-    </row>
-    <row r="334" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N333" s="3"/>
+    </row>
+    <row r="334" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>149</v>
       </c>
@@ -14643,11 +14914,11 @@
       <c r="I334" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K334" s="3"/>
       <c r="L334" s="3"/>
       <c r="M334" s="3"/>
-    </row>
-    <row r="335" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N334" s="3"/>
+    </row>
+    <row r="335" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>149</v>
       </c>
@@ -14675,11 +14946,11 @@
       <c r="I335" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="K335" s="3"/>
       <c r="L335" s="3"/>
       <c r="M335" s="3"/>
-    </row>
-    <row r="336" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N335" s="3"/>
+    </row>
+    <row r="336" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>150</v>
       </c>
@@ -14707,11 +14978,11 @@
       <c r="I336" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="K336" s="3"/>
       <c r="L336" s="3"/>
       <c r="M336" s="3"/>
-    </row>
-    <row r="337" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N336" s="3"/>
+    </row>
+    <row r="337" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>150</v>
       </c>
@@ -14739,11 +15010,11 @@
       <c r="I337" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="K337" s="3"/>
       <c r="L337" s="3"/>
       <c r="M337" s="3"/>
-    </row>
-    <row r="338" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N337" s="3"/>
+    </row>
+    <row r="338" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>151</v>
       </c>
@@ -14771,14 +15042,14 @@
       <c r="I338" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J338" s="2" t="s">
+      <c r="K338" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K338" s="3"/>
       <c r="L338" s="3"/>
       <c r="M338" s="3"/>
-    </row>
-    <row r="339" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N338" s="3"/>
+    </row>
+    <row r="339" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>151</v>
       </c>
@@ -14806,11 +15077,11 @@
       <c r="I339" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="K339" s="3"/>
       <c r="L339" s="3"/>
       <c r="M339" s="3"/>
-    </row>
-    <row r="340" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N339" s="3"/>
+    </row>
+    <row r="340" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>152</v>
       </c>
@@ -14820,11 +15091,11 @@
       <c r="C340" s="1">
         <v>15201</v>
       </c>
-      <c r="K340" s="6"/>
       <c r="L340" s="6"/>
       <c r="M340" s="6"/>
-    </row>
-    <row r="341" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N340" s="6"/>
+    </row>
+    <row r="341" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>153</v>
       </c>
@@ -14852,14 +15123,14 @@
       <c r="I341" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J341" s="2" t="s">
+      <c r="K341" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K341" s="3"/>
       <c r="L341" s="3"/>
       <c r="M341" s="3"/>
-    </row>
-    <row r="342" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N341" s="3"/>
+    </row>
+    <row r="342" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>154</v>
       </c>
@@ -14887,11 +15158,11 @@
       <c r="I342" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="K342" s="3"/>
       <c r="L342" s="3"/>
       <c r="M342" s="3"/>
-    </row>
-    <row r="343" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N342" s="3"/>
+    </row>
+    <row r="343" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>155</v>
       </c>
@@ -14919,14 +15190,14 @@
       <c r="I343" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J343" s="2" t="s">
+      <c r="K343" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K343" s="3"/>
       <c r="L343" s="3"/>
       <c r="M343" s="3"/>
-    </row>
-    <row r="344" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N343" s="3"/>
+    </row>
+    <row r="344" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>156</v>
       </c>
@@ -14954,14 +15225,14 @@
       <c r="I344" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J344" s="2" t="s">
+      <c r="K344" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K344" s="3"/>
       <c r="L344" s="3"/>
       <c r="M344" s="3"/>
-    </row>
-    <row r="345" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N344" s="3"/>
+    </row>
+    <row r="345" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>156</v>
       </c>
@@ -14989,14 +15260,14 @@
       <c r="I345" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J345" s="2" t="s">
+      <c r="K345" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K345" s="3"/>
       <c r="L345" s="3"/>
       <c r="M345" s="3"/>
-    </row>
-    <row r="346" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N345" s="3"/>
+    </row>
+    <row r="346" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>156</v>
       </c>
@@ -15024,14 +15295,14 @@
       <c r="I346" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J346" s="2" t="s">
+      <c r="K346" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K346" s="3"/>
       <c r="L346" s="3"/>
       <c r="M346" s="3"/>
-    </row>
-    <row r="347" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N346" s="3"/>
+    </row>
+    <row r="347" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>156</v>
       </c>
@@ -15059,14 +15330,14 @@
       <c r="I347" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J347" s="2" t="s">
+      <c r="K347" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K347" s="3"/>
       <c r="L347" s="3"/>
       <c r="M347" s="3"/>
-    </row>
-    <row r="348" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N347" s="3"/>
+    </row>
+    <row r="348" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>156</v>
       </c>
@@ -15094,14 +15365,14 @@
       <c r="I348" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="J348" s="2" t="s">
+      <c r="K348" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="K348" s="3"/>
       <c r="L348" s="3"/>
       <c r="M348" s="3"/>
-    </row>
-    <row r="349" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N348" s="3"/>
+    </row>
+    <row r="349" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>156</v>
       </c>
@@ -15129,11 +15400,11 @@
       <c r="I349" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="K349" s="3"/>
       <c r="L349" s="3"/>
       <c r="M349" s="3"/>
-    </row>
-    <row r="350" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N349" s="3"/>
+    </row>
+    <row r="350" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>157</v>
       </c>
@@ -15143,12 +15414,12 @@
       <c r="C350" s="1">
         <v>15701</v>
       </c>
-      <c r="K350" s="6"/>
       <c r="L350" s="6"/>
       <c r="M350" s="6"/>
+      <c r="N350" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J350" xr:uid="{21E7D8C5-59DB-465F-80B7-E6C364678A90}"/>
+  <autoFilter ref="A1:K350" xr:uid="{21E7D8C5-59DB-465F-80B7-E6C364678A90}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/inst/resources/reference_indicator_bank.xlsx
+++ b/inst/resources/reference_indicator_bank.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D08088C-6D28-4F59-94C4-2C9D6DFDD41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E72342D-F972-4C8C-93E1-976D7E79B076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_bank" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_bank!$A$1:$K$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_bank!$A$1:$L$350</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3474" uniqueCount="899">
   <si>
     <t>indicator_name</t>
   </si>
@@ -2674,6 +2674,75 @@
   </si>
   <si>
     <t>Main Water Source, Barriers to Water Access, Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
+  </si>
+  <si>
+    <t>data_collection_level</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Household</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Key Informant</t>
+  </si>
+  <si>
+    <t>Facility Staff</t>
+  </si>
+  <si>
+    <t>Sex, Age in Years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Informant </t>
+  </si>
+  <si>
+    <t>Facility Records</t>
+  </si>
+  <si>
+    <t>Water Container</t>
+  </si>
+  <si>
+    <t>Staff</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Herd</t>
+  </si>
+  <si>
+    <t>Barriers to Water Access, Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Shelter Type, Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Latrine</t>
+  </si>
+  <si>
+    <t>Water Point</t>
+  </si>
+  <si>
+    <t>Sex, Age in Months, Nutritional Status</t>
+  </si>
+  <si>
+    <t>Sex, Age in Years, Nutritional Status</t>
+  </si>
+  <si>
+    <t>Facility</t>
+  </si>
+  <si>
+    <t>Latrine Coverage, Sex of Head of Household, Marital Status of Head of Household, Dependency Ratio, Households with Member with Disability Status, Residency Status, Month of Arrival (for displaced)</t>
   </si>
 </sst>
 </file>
@@ -3071,7 +3140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F55F414-FB28-4448-AE5F-D8C818819F2A}">
-  <dimension ref="A1:N350"/>
+  <dimension ref="A1:O350"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -3082,13 +3151,13 @@
     <col min="7" max="7" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="47.42578125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="51.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="51.7109375" customWidth="1"/>
-    <col min="11" max="11" width="46.28515625" customWidth="1"/>
-    <col min="12" max="13" width="19" style="4" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" style="4" customWidth="1"/>
+    <col min="10" max="11" width="51.7109375" customWidth="1"/>
+    <col min="12" max="12" width="46.28515625" customWidth="1"/>
+    <col min="13" max="14" width="19" style="4" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -3120,19 +3189,22 @@
         <v>873</v>
       </c>
       <c r="K1" t="s">
+        <v>876</v>
+      </c>
+      <c r="L1" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -3163,8 +3235,8 @@
       <c r="J2" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>91</v>
+      <c r="K2" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>91</v>
@@ -3172,8 +3244,11 @@
       <c r="N2" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>101</v>
       </c>
@@ -3204,8 +3279,8 @@
       <c r="J3" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>91</v>
+      <c r="K3" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>91</v>
@@ -3213,8 +3288,11 @@
       <c r="N3" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>101</v>
       </c>
@@ -3245,8 +3323,8 @@
       <c r="J4" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>91</v>
+      <c r="K4" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>91</v>
@@ -3254,8 +3332,11 @@
       <c r="N4" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>101</v>
       </c>
@@ -3283,8 +3364,11 @@
       <c r="I5" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>91</v>
+      <c r="J5" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>91</v>
@@ -3292,8 +3376,11 @@
       <c r="N5" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>101</v>
       </c>
@@ -3321,8 +3408,11 @@
       <c r="I6" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>91</v>
+      <c r="J6" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>91</v>
@@ -3330,8 +3420,11 @@
       <c r="N6" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>101</v>
       </c>
@@ -3362,8 +3455,8 @@
       <c r="J7" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>91</v>
+      <c r="K7" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>91</v>
@@ -3371,8 +3464,11 @@
       <c r="N7" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>101</v>
       </c>
@@ -3403,8 +3499,8 @@
       <c r="J8" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>91</v>
+      <c r="K8" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>91</v>
@@ -3412,8 +3508,11 @@
       <c r="N8" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>101</v>
       </c>
@@ -3441,8 +3540,11 @@
       <c r="I9" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>91</v>
+      <c r="J9" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>91</v>
@@ -3450,8 +3552,11 @@
       <c r="N9" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>101</v>
       </c>
@@ -3479,8 +3584,11 @@
       <c r="I10" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>91</v>
+      <c r="J10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>91</v>
@@ -3488,8 +3596,11 @@
       <c r="N10" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>102</v>
       </c>
@@ -3517,8 +3628,11 @@
       <c r="I11" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>91</v>
+      <c r="J11" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>91</v>
@@ -3526,8 +3640,11 @@
       <c r="N11" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>102</v>
       </c>
@@ -3555,8 +3672,11 @@
       <c r="I12" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>91</v>
+      <c r="J12" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>91</v>
@@ -3564,8 +3684,11 @@
       <c r="N12" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>102</v>
       </c>
@@ -3593,8 +3716,11 @@
       <c r="I13" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>91</v>
+      <c r="J13" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>91</v>
@@ -3602,8 +3728,11 @@
       <c r="N13" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>102</v>
       </c>
@@ -3631,8 +3760,11 @@
       <c r="I14" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>91</v>
+      <c r="J14" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>91</v>
@@ -3640,8 +3772,11 @@
       <c r="N14" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>102</v>
       </c>
@@ -3669,8 +3804,11 @@
       <c r="I15" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>91</v>
+      <c r="J15" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>879</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>91</v>
@@ -3678,8 +3816,11 @@
       <c r="N15" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O15" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>103</v>
       </c>
@@ -3707,8 +3848,11 @@
       <c r="I16" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>91</v>
+      <c r="J16" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>91</v>
@@ -3716,8 +3860,11 @@
       <c r="N16" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>103</v>
       </c>
@@ -3745,20 +3892,26 @@
       <c r="I17" s="2" t="s">
         <v>355</v>
       </c>
+      <c r="J17" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K17" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>91</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O17" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>103</v>
       </c>
@@ -3786,8 +3939,11 @@
       <c r="I18" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>91</v>
+      <c r="J18" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>91</v>
@@ -3795,8 +3951,11 @@
       <c r="N18" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O18" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>103</v>
       </c>
@@ -3824,8 +3983,11 @@
       <c r="I19" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>91</v>
+      <c r="J19" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>91</v>
@@ -3833,8 +3995,11 @@
       <c r="N19" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>103</v>
       </c>
@@ -3862,8 +4027,11 @@
       <c r="I20" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>91</v>
+      <c r="J20" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>91</v>
@@ -3871,8 +4039,11 @@
       <c r="N20" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>103</v>
       </c>
@@ -3900,8 +4071,11 @@
       <c r="I21" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>91</v>
+      <c r="J21" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>91</v>
@@ -3909,8 +4083,11 @@
       <c r="N21" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>103</v>
       </c>
@@ -3938,8 +4115,11 @@
       <c r="I22" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>91</v>
+      <c r="J22" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>91</v>
@@ -3947,8 +4127,11 @@
       <c r="N22" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O22" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>103</v>
       </c>
@@ -3980,19 +4163,22 @@
         <v>867</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>0</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>103</v>
       </c>
@@ -4024,19 +4210,22 @@
         <v>867</v>
       </c>
       <c r="K24" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>103</v>
       </c>
@@ -4068,19 +4257,22 @@
         <v>867</v>
       </c>
       <c r="K25" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="M25" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>30</v>
       </c>
-      <c r="N25" s="3" t="s">
+      <c r="O25" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>103</v>
       </c>
@@ -4112,19 +4304,22 @@
         <v>867</v>
       </c>
       <c r="K26" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>50</v>
       </c>
-      <c r="N26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>103</v>
       </c>
@@ -4156,19 +4351,22 @@
         <v>867</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>0</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>103</v>
       </c>
@@ -4200,19 +4398,22 @@
         <v>867</v>
       </c>
       <c r="K28" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="M28" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>15</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="O28" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>103</v>
       </c>
@@ -4244,19 +4445,22 @@
         <v>867</v>
       </c>
       <c r="K29" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>30</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>103</v>
       </c>
@@ -4288,19 +4492,22 @@
         <v>867</v>
       </c>
       <c r="K30" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L30" s="3" t="s">
+      <c r="M30" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>50</v>
       </c>
-      <c r="N30" s="3" t="s">
+      <c r="O30" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>103</v>
       </c>
@@ -4332,19 +4539,22 @@
         <v>867</v>
       </c>
       <c r="K31" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="M31" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3" t="s">
+      <c r="O31" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>103</v>
       </c>
@@ -4376,19 +4586,22 @@
         <v>867</v>
       </c>
       <c r="K32" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="M32" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>103</v>
       </c>
@@ -4420,19 +4633,22 @@
         <v>867</v>
       </c>
       <c r="K33" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="M33" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30</v>
       </c>
-      <c r="N33" s="3" t="s">
+      <c r="O33" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>103</v>
       </c>
@@ -4464,19 +4680,22 @@
         <v>867</v>
       </c>
       <c r="K34" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M34" s="3">
+      <c r="N34" s="3">
         <v>50</v>
       </c>
-      <c r="N34" s="3" t="s">
+      <c r="O34" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>103</v>
       </c>
@@ -4508,19 +4727,22 @@
         <v>867</v>
       </c>
       <c r="K35" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="M35" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>0</v>
       </c>
-      <c r="N35" s="3" t="s">
+      <c r="O35" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>103</v>
       </c>
@@ -4552,19 +4774,22 @@
         <v>867</v>
       </c>
       <c r="K36" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M36" s="3">
+      <c r="N36" s="3">
         <v>15</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="O36" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>103</v>
       </c>
@@ -4596,19 +4821,22 @@
         <v>867</v>
       </c>
       <c r="K37" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M37" s="3">
+      <c r="N37" s="3">
         <v>30</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>103</v>
       </c>
@@ -4640,19 +4868,22 @@
         <v>867</v>
       </c>
       <c r="K38" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M38" s="3">
+      <c r="N38" s="3">
         <v>50</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="O38" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>104</v>
       </c>
@@ -4680,8 +4911,11 @@
       <c r="I39" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="L39" s="3" t="s">
-        <v>91</v>
+      <c r="J39" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>91</v>
@@ -4689,8 +4923,11 @@
       <c r="N39" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O39" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>104</v>
       </c>
@@ -4718,8 +4955,11 @@
       <c r="I40" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="L40" s="3" t="s">
-        <v>91</v>
+      <c r="J40" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>91</v>
@@ -4727,8 +4967,11 @@
       <c r="N40" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O40" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>104</v>
       </c>
@@ -4760,19 +5003,22 @@
         <v>867</v>
       </c>
       <c r="K41" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>91</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O41" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>105</v>
       </c>
@@ -4803,17 +5049,20 @@
       <c r="J42" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L42" s="3" t="s">
+      <c r="K42" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
+      <c r="O42" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>105</v>
       </c>
@@ -4844,17 +5093,20 @@
       <c r="J43" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L43" s="3" t="s">
+      <c r="K43" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>0.5</v>
       </c>
-      <c r="N43" s="3" t="s">
+      <c r="O43" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>105</v>
       </c>
@@ -4885,17 +5137,20 @@
       <c r="J44" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="K44" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="O44" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="45" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>105</v>
       </c>
@@ -4926,17 +5181,20 @@
       <c r="J45" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="K45" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2</v>
       </c>
-      <c r="N45" s="3" t="s">
+      <c r="O45" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>105</v>
       </c>
@@ -4967,17 +5225,20 @@
       <c r="J46" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L46" s="3" t="s">
+      <c r="K46" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3" t="s">
+      <c r="O46" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="47" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>105</v>
       </c>
@@ -5008,17 +5269,20 @@
       <c r="J47" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="K47" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1</v>
       </c>
-      <c r="N47" s="3" t="s">
+      <c r="O47" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="48" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>105</v>
       </c>
@@ -5049,17 +5313,20 @@
       <c r="J48" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L48" s="3" t="s">
+      <c r="K48" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="49" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>105</v>
       </c>
@@ -5090,17 +5357,20 @@
       <c r="J49" s="2" t="s">
         <v>868</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="K49" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4</v>
       </c>
-      <c r="N49" s="3" t="s">
+      <c r="O49" s="3" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="50" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>105</v>
       </c>
@@ -5128,13 +5398,19 @@
       <c r="I50" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="L50" s="3"/>
+      <c r="J50" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M50" s="3"/>
-      <c r="N50" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N50" s="3"/>
+      <c r="O50" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>106</v>
       </c>
@@ -5165,17 +5441,20 @@
       <c r="J51" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L51" s="3" t="s">
+      <c r="K51" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M51" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M51" s="3">
+      <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="5" t="s">
+      <c r="O51" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="52" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>106</v>
       </c>
@@ -5206,17 +5485,20 @@
       <c r="J52" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="K52" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10</v>
       </c>
-      <c r="N52" s="5" t="s">
+      <c r="O52" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="53" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>106</v>
       </c>
@@ -5247,17 +5529,20 @@
       <c r="J53" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="K53" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M53" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M53" s="3">
+      <c r="N53" s="3">
         <v>20</v>
       </c>
-      <c r="N53" s="5" t="s">
+      <c r="O53" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="54" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>106</v>
       </c>
@@ -5288,17 +5573,20 @@
       <c r="J54" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L54" s="3" t="s">
+      <c r="K54" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30</v>
       </c>
-      <c r="N54" s="5" t="s">
+      <c r="O54" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="55" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>106</v>
       </c>
@@ -5330,19 +5618,22 @@
         <v>867</v>
       </c>
       <c r="K55" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L55" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="M55" s="5" t="s">
         <v>91</v>
       </c>
       <c r="N55" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O55" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>106</v>
       </c>
@@ -5374,19 +5665,22 @@
         <v>867</v>
       </c>
       <c r="K56" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L56" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="M56" s="5" t="s">
         <v>91</v>
       </c>
       <c r="N56" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O56" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>106</v>
       </c>
@@ -5418,19 +5712,22 @@
         <v>867</v>
       </c>
       <c r="K57" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L57" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="M57" s="5" t="s">
         <v>91</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O57" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>106</v>
       </c>
@@ -5458,17 +5755,23 @@
       <c r="I58" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="J58" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="5" t="s">
+      <c r="O58" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="59" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>106</v>
       </c>
@@ -5496,17 +5799,23 @@
       <c r="I59" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="J59" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M59" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="5" t="s">
+      <c r="O59" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="60" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>106</v>
       </c>
@@ -5534,17 +5843,23 @@
       <c r="I60" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L60" s="3" t="s">
+      <c r="J60" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M60" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="5" t="s">
+      <c r="O60" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="61" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>106</v>
       </c>
@@ -5572,17 +5887,23 @@
       <c r="I61" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L61" s="3" t="s">
+      <c r="J61" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M61" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="5" t="s">
+      <c r="O61" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="62" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>106</v>
       </c>
@@ -5610,17 +5931,23 @@
       <c r="I62" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L62" s="3" t="s">
+      <c r="J62" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M62" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="5" t="s">
+      <c r="O62" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="63" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>106</v>
       </c>
@@ -5648,17 +5975,23 @@
       <c r="I63" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L63" s="3" t="s">
+      <c r="J63" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M63" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M63" s="3">
+      <c r="N63" s="3">
         <v>50</v>
       </c>
-      <c r="N63" s="5" t="s">
+      <c r="O63" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>106</v>
       </c>
@@ -5686,17 +6019,23 @@
       <c r="I64" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L64" s="3" t="s">
+      <c r="J64" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M64" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M64" s="3">
+      <c r="N64" s="3">
         <v>100</v>
       </c>
-      <c r="N64" s="5" t="s">
+      <c r="O64" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="65" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>106</v>
       </c>
@@ -5724,17 +6063,23 @@
       <c r="I65" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L65" s="3" t="s">
+      <c r="J65" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M65" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M65" s="3">
+      <c r="N65" s="3">
         <v>200</v>
       </c>
-      <c r="N65" s="5" t="s">
+      <c r="O65" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="66" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>106</v>
       </c>
@@ -5762,17 +6107,23 @@
       <c r="I66" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="J66" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>0</v>
       </c>
-      <c r="N66" s="5" t="s">
+      <c r="O66" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="67" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>106</v>
       </c>
@@ -5800,17 +6151,23 @@
       <c r="I67" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L67" s="3" t="s">
+      <c r="J67" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M67" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M67" s="3">
+      <c r="N67" s="3">
         <v>25</v>
       </c>
-      <c r="N67" s="5" t="s">
+      <c r="O67" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="68" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>106</v>
       </c>
@@ -5838,17 +6195,23 @@
       <c r="I68" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L68" s="3" t="s">
+      <c r="J68" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M68" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M68" s="3">
+      <c r="N68" s="3">
         <v>50</v>
       </c>
-      <c r="N68" s="5" t="s">
+      <c r="O68" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="69" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>106</v>
       </c>
@@ -5876,17 +6239,23 @@
       <c r="I69" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L69" s="3" t="s">
+      <c r="J69" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M69" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M69" s="3">
+      <c r="N69" s="3">
         <v>100</v>
       </c>
-      <c r="N69" s="5" t="s">
+      <c r="O69" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="70" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>106</v>
       </c>
@@ -5914,17 +6283,23 @@
       <c r="I70" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L70" s="3" t="s">
+      <c r="J70" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M70" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="5" t="s">
+      <c r="O70" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="71" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>106</v>
       </c>
@@ -5952,17 +6327,23 @@
       <c r="I71" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="J71" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M71" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M71" s="3">
+      <c r="N71" s="3">
         <v>50</v>
       </c>
-      <c r="N71" s="5" t="s">
+      <c r="O71" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="72" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>106</v>
       </c>
@@ -5990,17 +6371,23 @@
       <c r="I72" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L72" s="3" t="s">
+      <c r="J72" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M72" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>100</v>
       </c>
-      <c r="N72" s="5" t="s">
+      <c r="O72" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="73" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>106</v>
       </c>
@@ -6028,17 +6415,23 @@
       <c r="I73" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L73" s="3" t="s">
+      <c r="J73" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M73" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M73" s="3">
+      <c r="N73" s="3">
         <v>200</v>
       </c>
-      <c r="N73" s="5" t="s">
+      <c r="O73" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="74" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>106</v>
       </c>
@@ -6066,17 +6459,23 @@
       <c r="I74" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="L74" s="3" t="s">
-        <v>91</v>
+      <c r="J74" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>884</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N74" s="5" t="s">
+      <c r="N74" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O74" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="75" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>106</v>
       </c>
@@ -6104,17 +6503,23 @@
       <c r="I75" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="L75" s="3" t="s">
+      <c r="J75" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M75" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M75" s="3" t="s">
+      <c r="N75" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="N75" s="3" t="s">
+      <c r="O75" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="76" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>106</v>
       </c>
@@ -6142,17 +6547,23 @@
       <c r="I76" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="L76" s="3" t="s">
+      <c r="J76" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M76" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M76" s="3" t="s">
+      <c r="N76" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="N76" s="3" t="s">
+      <c r="O76" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="77" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>106</v>
       </c>
@@ -6180,17 +6591,23 @@
       <c r="I77" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="L77" s="3" t="s">
+      <c r="J77" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M77" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M77" s="3" t="s">
+      <c r="N77" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="N77" s="3" t="s">
+      <c r="O77" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="78" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>106</v>
       </c>
@@ -6218,17 +6635,23 @@
       <c r="I78" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L78" s="3" t="s">
+      <c r="J78" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M78" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M78" s="3">
+      <c r="N78" s="3">
         <v>0</v>
       </c>
-      <c r="N78" s="5" t="s">
+      <c r="O78" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="79" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>106</v>
       </c>
@@ -6256,17 +6679,23 @@
       <c r="I79" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L79" s="3" t="s">
+      <c r="J79" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M79" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M79" s="3">
+      <c r="N79" s="3">
         <v>100</v>
       </c>
-      <c r="N79" s="5" t="s">
+      <c r="O79" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="80" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>106</v>
       </c>
@@ -6294,17 +6723,23 @@
       <c r="I80" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L80" s="3" t="s">
+      <c r="J80" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M80" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M80" s="3">
+      <c r="N80" s="3">
         <v>200</v>
       </c>
-      <c r="N80" s="5" t="s">
+      <c r="O80" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="81" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>106</v>
       </c>
@@ -6332,17 +6767,23 @@
       <c r="I81" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L81" s="3" t="s">
+      <c r="J81" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M81" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="O81" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="82" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>106</v>
       </c>
@@ -6370,17 +6811,23 @@
       <c r="I82" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L82" s="3" t="s">
+      <c r="J82" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M82" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M82" s="3">
+      <c r="N82" s="3">
         <v>0</v>
       </c>
-      <c r="N82" s="5" t="s">
+      <c r="O82" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="83" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>106</v>
       </c>
@@ -6408,17 +6855,23 @@
       <c r="I83" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="J83" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>50</v>
       </c>
-      <c r="N83" s="5" t="s">
+      <c r="O83" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="84" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>106</v>
       </c>
@@ -6446,17 +6899,23 @@
       <c r="I84" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L84" s="3" t="s">
+      <c r="J84" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M84" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M84" s="3">
+      <c r="N84" s="3">
         <v>100</v>
       </c>
-      <c r="N84" s="5" t="s">
+      <c r="O84" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="85" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>106</v>
       </c>
@@ -6484,17 +6943,23 @@
       <c r="I85" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L85" s="3" t="s">
+      <c r="J85" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M85" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M85" s="3">
+      <c r="N85" s="3">
         <v>200</v>
       </c>
-      <c r="N85" s="5" t="s">
+      <c r="O85" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="86" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>106</v>
       </c>
@@ -6522,17 +6987,23 @@
       <c r="I86" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="L86" s="3" t="s">
+      <c r="J86" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M86" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M86" s="3">
+      <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="5" t="s">
+      <c r="O86" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="87" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>106</v>
       </c>
@@ -6560,17 +7031,23 @@
       <c r="I87" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="J87" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M87" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M87" s="3">
+      <c r="N87" s="3">
         <v>20</v>
       </c>
-      <c r="N87" s="5" t="s">
+      <c r="O87" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="88" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>106</v>
       </c>
@@ -6598,17 +7075,23 @@
       <c r="I88" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="J88" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M88" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M88" s="3">
+      <c r="N88" s="3">
         <v>30</v>
       </c>
-      <c r="N88" s="5" t="s">
+      <c r="O88" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="89" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>106</v>
       </c>
@@ -6636,17 +7119,23 @@
       <c r="I89" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="L89" s="3" t="s">
+      <c r="J89" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M89" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40</v>
       </c>
-      <c r="N89" s="5" t="s">
+      <c r="O89" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="90" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>106</v>
       </c>
@@ -6677,17 +7166,20 @@
       <c r="J90" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L90" s="3" t="s">
+      <c r="K90" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M90" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M90" s="3">
+      <c r="N90" s="3">
         <v>0</v>
       </c>
-      <c r="N90" s="5" t="s">
+      <c r="O90" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="91" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>106</v>
       </c>
@@ -6718,17 +7210,20 @@
       <c r="J91" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="K91" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M91" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>20</v>
       </c>
-      <c r="N91" s="5" t="s">
+      <c r="O91" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="92" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>106</v>
       </c>
@@ -6759,17 +7254,20 @@
       <c r="J92" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L92" s="3" t="s">
+      <c r="K92" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M92" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M92" s="3">
+      <c r="N92" s="3">
         <v>40</v>
       </c>
-      <c r="N92" s="5" t="s">
+      <c r="O92" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="93" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>106</v>
       </c>
@@ -6800,17 +7298,20 @@
       <c r="J93" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="L93" s="3" t="s">
+      <c r="K93" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M93" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M93" s="3">
+      <c r="N93" s="3">
         <v>50</v>
       </c>
-      <c r="N93" s="5" t="s">
+      <c r="O93" s="5" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="94" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>107</v>
       </c>
@@ -6841,17 +7342,20 @@
       <c r="J94" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="K94" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M94" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="95" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>107</v>
       </c>
@@ -6882,17 +7386,20 @@
       <c r="J95" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L95" s="3" t="s">
+      <c r="K95" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M95" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M95" s="3">
+      <c r="N95" s="3">
         <v>5</v>
       </c>
-      <c r="N95" s="3" t="s">
+      <c r="O95" s="3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="96" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>107</v>
       </c>
@@ -6923,17 +7430,20 @@
       <c r="J96" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="K96" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M96" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>10</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="97" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>107</v>
       </c>
@@ -6964,17 +7474,20 @@
       <c r="J97" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L97" s="3" t="s">
+      <c r="K97" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M97" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M97" s="3">
+      <c r="N97" s="3">
         <v>15</v>
       </c>
-      <c r="N97" s="3" t="s">
+      <c r="O97" s="3" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="98" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>107</v>
       </c>
@@ -7005,17 +7518,20 @@
       <c r="J98" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="L98" s="3" t="s">
+      <c r="K98" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M98" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M98" s="3">
+      <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3" t="s">
+      <c r="O98" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="99" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>107</v>
       </c>
@@ -7046,17 +7562,20 @@
       <c r="J99" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="L99" s="3" t="s">
+      <c r="K99" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M99" s="3">
+      <c r="N99" s="3">
         <v>10</v>
       </c>
-      <c r="N99" s="3" t="s">
+      <c r="O99" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="100" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>107</v>
       </c>
@@ -7087,17 +7606,20 @@
       <c r="J100" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="K100" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M100" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>20</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="101" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>107</v>
       </c>
@@ -7128,17 +7650,20 @@
       <c r="J101" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="K101" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M101" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>30</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="102" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>107</v>
       </c>
@@ -7166,17 +7691,23 @@
       <c r="I102" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L102" s="3" t="s">
+      <c r="J102" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M102" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="N102" s="3" t="s">
+      <c r="O102" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="103" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>107</v>
       </c>
@@ -7204,17 +7735,23 @@
       <c r="I103" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L103" s="3" t="s">
+      <c r="J103" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M103" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M103" s="3" t="s">
+      <c r="N103" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="N103" s="3" t="s">
+      <c r="O103" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="104" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>107</v>
       </c>
@@ -7242,17 +7779,23 @@
       <c r="I104" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L104" s="3" t="s">
+      <c r="J104" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M104" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M104" s="3" t="s">
+      <c r="N104" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="N104" s="3" t="s">
+      <c r="O104" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="105" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>107</v>
       </c>
@@ -7283,17 +7826,20 @@
       <c r="J105" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L105" s="3" t="s">
+      <c r="K105" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M105" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="M105" s="3">
+      <c r="N105" s="3">
         <v>0</v>
       </c>
-      <c r="N105" s="3" t="s">
+      <c r="O105" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="106" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>107</v>
       </c>
@@ -7324,17 +7870,20 @@
       <c r="J106" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L106" s="3" t="s">
+      <c r="K106" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M106" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M106" s="3">
+      <c r="N106" s="3">
         <v>5</v>
       </c>
-      <c r="N106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="107" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -7365,17 +7914,20 @@
       <c r="J107" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L107" s="3" t="s">
+      <c r="K107" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M107" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M107" s="3">
+      <c r="N107" s="3">
         <v>10</v>
       </c>
-      <c r="N107" s="3" t="s">
+      <c r="O107" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="108" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -7406,17 +7958,20 @@
       <c r="J108" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L108" s="3" t="s">
+      <c r="K108" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M108" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M108" s="3">
+      <c r="N108" s="3">
         <v>15</v>
       </c>
-      <c r="N108" s="3" t="s">
+      <c r="O108" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="109" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -7447,17 +8002,20 @@
       <c r="J109" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="L109" s="3" t="s">
+      <c r="K109" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="M109" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M109" s="3">
+      <c r="N109" s="3">
         <v>30</v>
       </c>
-      <c r="N109" s="3" t="s">
+      <c r="O109" s="3" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="110" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>107</v>
       </c>
@@ -7485,17 +8043,23 @@
       <c r="I110" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L110" s="3" t="s">
+      <c r="J110" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M110" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M110" s="3">
+      <c r="N110" s="3">
         <v>0</v>
       </c>
-      <c r="N110" s="3" t="s">
+      <c r="O110" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="111" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>107</v>
       </c>
@@ -7523,17 +8087,23 @@
       <c r="I111" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L111" s="3" t="s">
+      <c r="J111" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M111" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M111" s="3">
+      <c r="N111" s="3">
         <v>20</v>
       </c>
-      <c r="N111" s="3" t="s">
+      <c r="O111" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="112" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>107</v>
       </c>
@@ -7561,17 +8131,23 @@
       <c r="I112" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L112" s="3" t="s">
+      <c r="J112" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M112" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M112" s="3">
+      <c r="N112" s="3">
         <v>30</v>
       </c>
-      <c r="N112" s="3" t="s">
+      <c r="O112" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="113" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>107</v>
       </c>
@@ -7599,17 +8175,23 @@
       <c r="I113" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L113" s="3" t="s">
+      <c r="J113" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="M113" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M113" s="3">
+      <c r="N113" s="3">
         <v>45</v>
       </c>
-      <c r="N113" s="3" t="s">
+      <c r="O113" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="114" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>108</v>
       </c>
@@ -7641,19 +8223,22 @@
         <v>869</v>
       </c>
       <c r="K114" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="L114" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="L114" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M114" s="3" t="s">
         <v>91</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O114" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>108</v>
       </c>
@@ -7685,19 +8270,22 @@
         <v>869</v>
       </c>
       <c r="K115" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="L115" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="L115" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M115" s="3" t="s">
         <v>91</v>
       </c>
       <c r="N115" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O115" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>109</v>
       </c>
@@ -7728,8 +8316,8 @@
       <c r="J116" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="L116" s="3" t="s">
-        <v>91</v>
+      <c r="K116" s="2" t="s">
+        <v>885</v>
       </c>
       <c r="M116" s="3" t="s">
         <v>91</v>
@@ -7737,8 +8325,11 @@
       <c r="N116" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O116" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>109</v>
       </c>
@@ -7769,17 +8360,20 @@
       <c r="J117" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="L117" s="3" t="s">
+      <c r="K117" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="M117" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M117" s="3">
+      <c r="N117" s="3">
         <v>10</v>
       </c>
-      <c r="N117" s="3" t="s">
+      <c r="O117" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="118" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>109</v>
       </c>
@@ -7810,17 +8404,20 @@
       <c r="J118" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="L118" s="3" t="s">
+      <c r="K118" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="M118" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M118" s="3">
+      <c r="N118" s="3">
         <v>30</v>
       </c>
-      <c r="N118" s="3" t="s">
+      <c r="O118" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="119" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>109</v>
       </c>
@@ -7851,17 +8448,20 @@
       <c r="J119" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="L119" s="3" t="s">
+      <c r="K119" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="M119" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M119" s="3">
+      <c r="N119" s="3">
         <v>50</v>
       </c>
-      <c r="N119" s="3" t="s">
+      <c r="O119" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="120" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>109</v>
       </c>
@@ -7892,17 +8492,20 @@
       <c r="J120" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="L120" s="3" t="s">
+      <c r="K120" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="M120" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M120" s="3">
+      <c r="N120" s="3">
         <v>70</v>
       </c>
-      <c r="N120" s="3" t="s">
+      <c r="O120" s="3" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="121" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>110</v>
       </c>
@@ -7912,11 +8515,11 @@
       <c r="C121" s="1">
         <v>11001</v>
       </c>
-      <c r="L121" s="6"/>
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
-    </row>
-    <row r="122" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O121" s="6"/>
+    </row>
+    <row r="122" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>111</v>
       </c>
@@ -7947,11 +8550,14 @@
       <c r="J122" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="L122" s="3"/>
+      <c r="K122" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
-    </row>
-    <row r="123" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O122" s="3"/>
+    </row>
+    <row r="123" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>111</v>
       </c>
@@ -7982,11 +8588,14 @@
       <c r="J123" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="L123" s="3"/>
+      <c r="K123" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
-    </row>
-    <row r="124" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O123" s="3"/>
+    </row>
+    <row r="124" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>111</v>
       </c>
@@ -8018,13 +8627,16 @@
         <v>867</v>
       </c>
       <c r="K124" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L124" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L124" s="3"/>
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
-    </row>
-    <row r="125" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O124" s="3"/>
+    </row>
+    <row r="125" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>112</v>
       </c>
@@ -8052,11 +8664,17 @@
       <c r="I125" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="L125" s="3"/>
+      <c r="J125" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
-    </row>
-    <row r="126" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O125" s="3"/>
+    </row>
+    <row r="126" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>112</v>
       </c>
@@ -8084,11 +8702,17 @@
       <c r="I126" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="L126" s="3"/>
+      <c r="J126" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
-    </row>
-    <row r="127" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O126" s="3"/>
+    </row>
+    <row r="127" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>112</v>
       </c>
@@ -8116,11 +8740,17 @@
       <c r="I127" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="L127" s="3"/>
+      <c r="J127" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
-    </row>
-    <row r="128" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O127" s="3"/>
+    </row>
+    <row r="128" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>112</v>
       </c>
@@ -8148,11 +8778,17 @@
       <c r="I128" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="L128" s="3"/>
+      <c r="J128" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
-    </row>
-    <row r="129" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O128" s="3"/>
+    </row>
+    <row r="129" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>112</v>
       </c>
@@ -8180,11 +8816,17 @@
       <c r="I129" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="L129" s="3"/>
+      <c r="J129" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
-    </row>
-    <row r="130" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O129" s="3"/>
+    </row>
+    <row r="130" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>112</v>
       </c>
@@ -8212,11 +8854,17 @@
       <c r="I130" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="L130" s="3"/>
+      <c r="J130" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
-    </row>
-    <row r="131" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O130" s="3"/>
+    </row>
+    <row r="131" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>113</v>
       </c>
@@ -8244,11 +8892,17 @@
       <c r="I131" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="L131" s="3"/>
+      <c r="J131" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
-    </row>
-    <row r="132" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O131" s="3"/>
+    </row>
+    <row r="132" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>113</v>
       </c>
@@ -8280,13 +8934,16 @@
         <v>867</v>
       </c>
       <c r="K132" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L132" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L132" s="3"/>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
-    </row>
-    <row r="133" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O132" s="3"/>
+    </row>
+    <row r="133" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>113</v>
       </c>
@@ -8314,11 +8971,17 @@
       <c r="I133" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="L133" s="3"/>
+      <c r="J133" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
-    </row>
-    <row r="134" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O133" s="3"/>
+    </row>
+    <row r="134" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>113</v>
       </c>
@@ -8346,11 +9009,17 @@
       <c r="I134" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="L134" s="3"/>
+      <c r="J134" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
-    </row>
-    <row r="135" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O134" s="3"/>
+    </row>
+    <row r="135" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>113</v>
       </c>
@@ -8378,14 +9047,20 @@
       <c r="I135" s="2" t="s">
         <v>790</v>
       </c>
+      <c r="J135" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K135" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L135" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
-    </row>
-    <row r="136" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O135" s="3"/>
+    </row>
+    <row r="136" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>113</v>
       </c>
@@ -8413,14 +9088,20 @@
       <c r="I136" s="2" t="s">
         <v>790</v>
       </c>
+      <c r="J136" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K136" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L136" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
-    </row>
-    <row r="137" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O136" s="3"/>
+    </row>
+    <row r="137" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>113</v>
       </c>
@@ -8448,14 +9129,20 @@
       <c r="I137" s="2" t="s">
         <v>788</v>
       </c>
+      <c r="J137" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K137" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L137" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L137" s="3"/>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
-    </row>
-    <row r="138" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O137" s="3"/>
+    </row>
+    <row r="138" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>113</v>
       </c>
@@ -8483,14 +9170,20 @@
       <c r="I138" s="2" t="s">
         <v>788</v>
       </c>
+      <c r="J138" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K138" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L138" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L138" s="3"/>
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
-    </row>
-    <row r="139" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O138" s="3"/>
+    </row>
+    <row r="139" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>113</v>
       </c>
@@ -8518,14 +9211,20 @@
       <c r="I139" s="2" t="s">
         <v>789</v>
       </c>
+      <c r="J139" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K139" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L139" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
-    </row>
-    <row r="140" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O139" s="3"/>
+    </row>
+    <row r="140" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>113</v>
       </c>
@@ -8553,14 +9252,20 @@
       <c r="I140" s="2" t="s">
         <v>789</v>
       </c>
+      <c r="J140" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K140" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L140" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L140" s="3"/>
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
-    </row>
-    <row r="141" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O140" s="3"/>
+    </row>
+    <row r="141" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>113</v>
       </c>
@@ -8588,14 +9293,20 @@
       <c r="I141" s="2" t="s">
         <v>789</v>
       </c>
+      <c r="J141" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K141" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L141" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L141" s="3"/>
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
-    </row>
-    <row r="142" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O141" s="3"/>
+    </row>
+    <row r="142" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>113</v>
       </c>
@@ -8623,14 +9334,20 @@
       <c r="I142" s="2" t="s">
         <v>789</v>
       </c>
+      <c r="J142" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K142" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="L142" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
-    </row>
-    <row r="143" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O142" s="3"/>
+    </row>
+    <row r="143" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>113</v>
       </c>
@@ -8658,14 +9375,20 @@
       <c r="I143" s="2" t="s">
         <v>792</v>
       </c>
+      <c r="J143" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K143" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L143" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L143" s="3"/>
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
-    </row>
-    <row r="144" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O143" s="3"/>
+    </row>
+    <row r="144" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>113</v>
       </c>
@@ -8693,14 +9416,20 @@
       <c r="I144" s="2" t="s">
         <v>792</v>
       </c>
+      <c r="J144" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K144" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L144" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
-    </row>
-    <row r="145" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O144" s="3"/>
+    </row>
+    <row r="145" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>113</v>
       </c>
@@ -8728,14 +9457,20 @@
       <c r="I145" s="2" t="s">
         <v>791</v>
       </c>
+      <c r="J145" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K145" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L145" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L145" s="3"/>
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
-    </row>
-    <row r="146" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O145" s="3"/>
+    </row>
+    <row r="146" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>113</v>
       </c>
@@ -8763,14 +9498,20 @@
       <c r="I146" s="2" t="s">
         <v>791</v>
       </c>
+      <c r="J146" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K146" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L146" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L146" s="3"/>
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
-    </row>
-    <row r="147" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O146" s="3"/>
+    </row>
+    <row r="147" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>113</v>
       </c>
@@ -8798,14 +9539,20 @@
       <c r="I147" s="2" t="s">
         <v>791</v>
       </c>
+      <c r="J147" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K147" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L147" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
-    </row>
-    <row r="148" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O147" s="3"/>
+    </row>
+    <row r="148" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>113</v>
       </c>
@@ -8833,14 +9580,20 @@
       <c r="I148" s="2" t="s">
         <v>792</v>
       </c>
+      <c r="J148" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K148" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L148" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L148" s="3"/>
       <c r="M148" s="3"/>
       <c r="N148" s="3"/>
-    </row>
-    <row r="149" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O148" s="3"/>
+    </row>
+    <row r="149" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>113</v>
       </c>
@@ -8868,14 +9621,20 @@
       <c r="I149" s="2" t="s">
         <v>793</v>
       </c>
+      <c r="J149" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K149" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L149" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L149" s="3"/>
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
-    </row>
-    <row r="150" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O149" s="3"/>
+    </row>
+    <row r="150" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>113</v>
       </c>
@@ -8903,14 +9662,20 @@
       <c r="I150" s="2" t="s">
         <v>794</v>
       </c>
+      <c r="J150" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K150" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="L150" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3"/>
-    </row>
-    <row r="151" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O150" s="3"/>
+    </row>
+    <row r="151" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>114</v>
       </c>
@@ -8941,11 +9706,14 @@
       <c r="J151" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="L151" s="3"/>
+      <c r="K151" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
-    </row>
-    <row r="152" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O151" s="3"/>
+    </row>
+    <row r="152" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>114</v>
       </c>
@@ -8977,13 +9745,16 @@
         <v>869</v>
       </c>
       <c r="K152" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="L152" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="L152" s="3"/>
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
-    </row>
-    <row r="153" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O152" s="3"/>
+    </row>
+    <row r="153" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>114</v>
       </c>
@@ -9015,13 +9786,16 @@
         <v>869</v>
       </c>
       <c r="K153" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="L153" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="L153" s="3"/>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
-    </row>
-    <row r="154" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O153" s="3"/>
+    </row>
+    <row r="154" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>114</v>
       </c>
@@ -9049,11 +9823,17 @@
       <c r="I154" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="L154" s="3"/>
+      <c r="J154" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
-    </row>
-    <row r="155" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O154" s="3"/>
+    </row>
+    <row r="155" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>114</v>
       </c>
@@ -9081,11 +9861,17 @@
       <c r="I155" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="L155" s="3"/>
+      <c r="J155" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
-    </row>
-    <row r="156" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O155" s="3"/>
+    </row>
+    <row r="156" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>114</v>
       </c>
@@ -9113,11 +9899,17 @@
       <c r="I156" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="L156" s="3"/>
+      <c r="J156" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M156" s="3"/>
       <c r="N156" s="3"/>
-    </row>
-    <row r="157" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O156" s="3"/>
+    </row>
+    <row r="157" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>115</v>
       </c>
@@ -9148,11 +9940,11 @@
       <c r="J157" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="L157" s="3"/>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
-    </row>
-    <row r="158" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O157" s="3"/>
+    </row>
+    <row r="158" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>115</v>
       </c>
@@ -9183,11 +9975,11 @@
       <c r="J158" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="L158" s="3"/>
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
-    </row>
-    <row r="159" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O158" s="3"/>
+    </row>
+    <row r="159" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>115</v>
       </c>
@@ -9218,11 +10010,11 @@
       <c r="J159" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="L159" s="3"/>
       <c r="M159" s="3"/>
       <c r="N159" s="3"/>
-    </row>
-    <row r="160" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O159" s="3"/>
+    </row>
+    <row r="160" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>115</v>
       </c>
@@ -9253,11 +10045,11 @@
       <c r="J160" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="L160" s="3"/>
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
-    </row>
-    <row r="161" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O160" s="3"/>
+    </row>
+    <row r="161" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>116</v>
       </c>
@@ -9267,11 +10059,11 @@
       <c r="C161" s="1">
         <v>11601</v>
       </c>
-      <c r="L161" s="6"/>
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
-    </row>
-    <row r="162" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O161" s="6"/>
+    </row>
+    <row r="162" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>117</v>
       </c>
@@ -9302,11 +10094,11 @@
       <c r="J162" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="L162" s="3"/>
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
-    </row>
-    <row r="163" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O162" s="3"/>
+    </row>
+    <row r="163" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>117</v>
       </c>
@@ -9334,11 +10126,17 @@
       <c r="I163" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="L163" s="3"/>
+      <c r="J163" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
-    </row>
-    <row r="164" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O163" s="3"/>
+    </row>
+    <row r="164" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>117</v>
       </c>
@@ -9366,11 +10164,17 @@
       <c r="I164" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="L164" s="3"/>
+      <c r="J164" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
-    </row>
-    <row r="165" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O164" s="3"/>
+    </row>
+    <row r="165" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>118</v>
       </c>
@@ -9398,14 +10202,20 @@
       <c r="I165" s="2" t="s">
         <v>679</v>
       </c>
+      <c r="J165" s="2" t="s">
+        <v>889</v>
+      </c>
       <c r="K165" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L165" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L165" s="3"/>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
-    </row>
-    <row r="166" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O165" s="3"/>
+    </row>
+    <row r="166" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>118</v>
       </c>
@@ -9433,14 +10243,20 @@
       <c r="I166" s="2" t="s">
         <v>679</v>
       </c>
+      <c r="J166" s="2" t="s">
+        <v>889</v>
+      </c>
       <c r="K166" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L166" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L166" s="3"/>
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
-    </row>
-    <row r="167" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O166" s="3"/>
+    </row>
+    <row r="167" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>118</v>
       </c>
@@ -9468,14 +10284,20 @@
       <c r="I167" s="2" t="s">
         <v>651</v>
       </c>
+      <c r="J167" s="2" t="s">
+        <v>875</v>
+      </c>
       <c r="K167" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L167" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L167" s="3"/>
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
-    </row>
-    <row r="168" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O167" s="3"/>
+    </row>
+    <row r="168" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>119</v>
       </c>
@@ -9503,14 +10325,20 @@
       <c r="I168" s="2" t="s">
         <v>653</v>
       </c>
+      <c r="J168" s="2" t="s">
+        <v>875</v>
+      </c>
       <c r="K168" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L168" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L168" s="3"/>
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
-    </row>
-    <row r="169" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O168" s="3"/>
+    </row>
+    <row r="169" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>119</v>
       </c>
@@ -9538,14 +10366,20 @@
       <c r="I169" s="2" t="s">
         <v>653</v>
       </c>
+      <c r="J169" s="2" t="s">
+        <v>875</v>
+      </c>
       <c r="K169" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L169" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
-    </row>
-    <row r="170" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O169" s="3"/>
+    </row>
+    <row r="170" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>120</v>
       </c>
@@ -9573,11 +10407,17 @@
       <c r="I170" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="L170" s="3"/>
+      <c r="J170" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M170" s="3"/>
       <c r="N170" s="3"/>
-    </row>
-    <row r="171" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O170" s="3"/>
+    </row>
+    <row r="171" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>120</v>
       </c>
@@ -9605,11 +10445,17 @@
       <c r="I171" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="L171" s="3"/>
+      <c r="J171" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
-    </row>
-    <row r="172" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O171" s="3"/>
+    </row>
+    <row r="172" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>120</v>
       </c>
@@ -9637,11 +10483,17 @@
       <c r="I172" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="L172" s="3"/>
+      <c r="J172" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
-    </row>
-    <row r="173" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O172" s="3"/>
+    </row>
+    <row r="173" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>120</v>
       </c>
@@ -9669,11 +10521,17 @@
       <c r="I173" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="L173" s="3"/>
+      <c r="J173" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
-    </row>
-    <row r="174" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O173" s="3"/>
+    </row>
+    <row r="174" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>120</v>
       </c>
@@ -9701,11 +10559,17 @@
       <c r="I174" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="L174" s="3"/>
+      <c r="J174" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
-    </row>
-    <row r="175" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O174" s="3"/>
+    </row>
+    <row r="175" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>121</v>
       </c>
@@ -9733,11 +10597,17 @@
       <c r="I175" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="L175" s="3"/>
+      <c r="J175" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3"/>
-    </row>
-    <row r="176" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O175" s="3"/>
+    </row>
+    <row r="176" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>122</v>
       </c>
@@ -9765,11 +10635,17 @@
       <c r="I176" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="L176" s="3"/>
+      <c r="J176" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3"/>
-    </row>
-    <row r="177" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O176" s="3"/>
+    </row>
+    <row r="177" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>122</v>
       </c>
@@ -9801,13 +10677,16 @@
         <v>867</v>
       </c>
       <c r="K177" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L177" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L177" s="3"/>
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
-    </row>
-    <row r="178" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O177" s="3"/>
+    </row>
+    <row r="178" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>123</v>
       </c>
@@ -9835,11 +10714,17 @@
       <c r="I178" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="L178" s="3"/>
+      <c r="J178" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M178" s="3"/>
       <c r="N178" s="3"/>
-    </row>
-    <row r="179" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O178" s="3"/>
+    </row>
+    <row r="179" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>123</v>
       </c>
@@ -9867,11 +10752,17 @@
       <c r="I179" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="L179" s="3"/>
+      <c r="J179" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M179" s="3"/>
       <c r="N179" s="3"/>
-    </row>
-    <row r="180" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O179" s="3"/>
+    </row>
+    <row r="180" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>123</v>
       </c>
@@ -9899,11 +10790,17 @@
       <c r="I180" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="L180" s="3"/>
+      <c r="J180" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
-    </row>
-    <row r="181" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O180" s="3"/>
+    </row>
+    <row r="181" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>123</v>
       </c>
@@ -9935,13 +10832,16 @@
         <v>867</v>
       </c>
       <c r="K181" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L181" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L181" s="3"/>
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
-    </row>
-    <row r="182" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O181" s="3"/>
+    </row>
+    <row r="182" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>123</v>
       </c>
@@ -9969,11 +10869,17 @@
       <c r="I182" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="L182" s="3"/>
+      <c r="J182" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
-    </row>
-    <row r="183" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O182" s="3"/>
+    </row>
+    <row r="183" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>123</v>
       </c>
@@ -10001,11 +10907,17 @@
       <c r="I183" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="L183" s="3"/>
+      <c r="J183" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M183" s="3"/>
       <c r="N183" s="3"/>
-    </row>
-    <row r="184" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O183" s="3"/>
+    </row>
+    <row r="184" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>123</v>
       </c>
@@ -10033,11 +10945,17 @@
       <c r="I184" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="L184" s="3"/>
+      <c r="J184" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K184" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M184" s="3"/>
       <c r="N184" s="3"/>
-    </row>
-    <row r="185" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O184" s="3"/>
+    </row>
+    <row r="185" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>124</v>
       </c>
@@ -10047,11 +10965,11 @@
       <c r="C185" s="1">
         <v>12401</v>
       </c>
-      <c r="L185" s="6"/>
       <c r="M185" s="6"/>
       <c r="N185" s="6"/>
-    </row>
-    <row r="186" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O185" s="6"/>
+    </row>
+    <row r="186" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>125</v>
       </c>
@@ -10079,11 +10997,17 @@
       <c r="I186" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="L186" s="3"/>
+      <c r="J186" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M186" s="3"/>
       <c r="N186" s="3"/>
-    </row>
-    <row r="187" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O186" s="3"/>
+    </row>
+    <row r="187" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>125</v>
       </c>
@@ -10111,11 +11035,17 @@
       <c r="I187" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="L187" s="3"/>
+      <c r="J187" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M187" s="3"/>
       <c r="N187" s="3"/>
-    </row>
-    <row r="188" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O187" s="3"/>
+    </row>
+    <row r="188" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>125</v>
       </c>
@@ -10143,11 +11073,17 @@
       <c r="I188" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="L188" s="3"/>
+      <c r="J188" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M188" s="3"/>
       <c r="N188" s="3"/>
-    </row>
-    <row r="189" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O188" s="3"/>
+    </row>
+    <row r="189" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>125</v>
       </c>
@@ -10179,13 +11115,16 @@
         <v>867</v>
       </c>
       <c r="K189" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L189" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L189" s="3"/>
       <c r="M189" s="3"/>
       <c r="N189" s="3"/>
-    </row>
-    <row r="190" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O189" s="3"/>
+    </row>
+    <row r="190" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>125</v>
       </c>
@@ -10217,13 +11156,16 @@
         <v>867</v>
       </c>
       <c r="K190" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L190" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L190" s="3"/>
       <c r="M190" s="3"/>
       <c r="N190" s="3"/>
-    </row>
-    <row r="191" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O190" s="3"/>
+    </row>
+    <row r="191" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>126</v>
       </c>
@@ -10251,11 +11193,17 @@
       <c r="I191" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="L191" s="3"/>
+      <c r="J191" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M191" s="3"/>
       <c r="N191" s="3"/>
-    </row>
-    <row r="192" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O191" s="3"/>
+    </row>
+    <row r="192" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>126</v>
       </c>
@@ -10283,11 +11231,17 @@
       <c r="I192" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="L192" s="3"/>
+      <c r="J192" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M192" s="3"/>
       <c r="N192" s="3"/>
-    </row>
-    <row r="193" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O192" s="3"/>
+    </row>
+    <row r="193" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>127</v>
       </c>
@@ -10315,11 +11269,17 @@
       <c r="I193" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="L193" s="3"/>
+      <c r="J193" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M193" s="3"/>
       <c r="N193" s="3"/>
-    </row>
-    <row r="194" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O193" s="3"/>
+    </row>
+    <row r="194" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>127</v>
       </c>
@@ -10347,11 +11307,14 @@
       <c r="I194" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="L194" s="3"/>
+      <c r="J194" s="2" t="s">
+        <v>891</v>
+      </c>
       <c r="M194" s="3"/>
       <c r="N194" s="3"/>
-    </row>
-    <row r="195" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O194" s="3"/>
+    </row>
+    <row r="195" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>128</v>
       </c>
@@ -10379,11 +11342,17 @@
       <c r="I195" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="L195" s="3"/>
+      <c r="J195" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M195" s="3"/>
       <c r="N195" s="3"/>
-    </row>
-    <row r="196" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O195" s="3"/>
+    </row>
+    <row r="196" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>129</v>
       </c>
@@ -10411,11 +11380,17 @@
       <c r="I196" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="L196" s="3"/>
+      <c r="J196" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M196" s="3"/>
       <c r="N196" s="3"/>
-    </row>
-    <row r="197" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O196" s="3"/>
+    </row>
+    <row r="197" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>130</v>
       </c>
@@ -10443,11 +11418,17 @@
       <c r="I197" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="L197" s="3"/>
+      <c r="J197" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M197" s="3"/>
       <c r="N197" s="3"/>
-    </row>
-    <row r="198" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O197" s="3"/>
+    </row>
+    <row r="198" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>130</v>
       </c>
@@ -10475,11 +11456,17 @@
       <c r="I198" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="L198" s="3"/>
+      <c r="J198" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K198" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M198" s="3"/>
       <c r="N198" s="3"/>
-    </row>
-    <row r="199" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O198" s="3"/>
+    </row>
+    <row r="199" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>131</v>
       </c>
@@ -10507,11 +11494,17 @@
       <c r="I199" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="L199" s="3"/>
+      <c r="J199" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K199" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M199" s="3"/>
       <c r="N199" s="3"/>
-    </row>
-    <row r="200" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O199" s="3"/>
+    </row>
+    <row r="200" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>131</v>
       </c>
@@ -10539,11 +11532,17 @@
       <c r="I200" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="L200" s="3"/>
+      <c r="J200" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K200" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M200" s="3"/>
       <c r="N200" s="3"/>
-    </row>
-    <row r="201" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O200" s="3"/>
+    </row>
+    <row r="201" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>131</v>
       </c>
@@ -10571,11 +11570,17 @@
       <c r="I201" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="L201" s="3"/>
+      <c r="J201" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K201" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M201" s="3"/>
       <c r="N201" s="3"/>
-    </row>
-    <row r="202" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O201" s="3"/>
+    </row>
+    <row r="202" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>131</v>
       </c>
@@ -10603,11 +11608,17 @@
       <c r="I202" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="L202" s="3"/>
+      <c r="J202" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K202" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M202" s="3"/>
       <c r="N202" s="3"/>
-    </row>
-    <row r="203" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O202" s="3"/>
+    </row>
+    <row r="203" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>131</v>
       </c>
@@ -10635,11 +11646,17 @@
       <c r="I203" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="L203" s="3"/>
+      <c r="J203" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K203" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M203" s="3"/>
       <c r="N203" s="3"/>
-    </row>
-    <row r="204" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O203" s="3"/>
+    </row>
+    <row r="204" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>132</v>
       </c>
@@ -10667,11 +11684,17 @@
       <c r="I204" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="L204" s="3"/>
+      <c r="J204" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M204" s="3"/>
       <c r="N204" s="3"/>
-    </row>
-    <row r="205" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O204" s="3"/>
+    </row>
+    <row r="205" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>132</v>
       </c>
@@ -10699,11 +11722,17 @@
       <c r="I205" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="L205" s="3"/>
+      <c r="J205" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K205" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M205" s="3"/>
       <c r="N205" s="3"/>
-    </row>
-    <row r="206" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O205" s="3"/>
+    </row>
+    <row r="206" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>132</v>
       </c>
@@ -10731,11 +11760,17 @@
       <c r="I206" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="L206" s="3"/>
+      <c r="J206" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>892</v>
+      </c>
       <c r="M206" s="3"/>
       <c r="N206" s="3"/>
-    </row>
-    <row r="207" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O206" s="3"/>
+    </row>
+    <row r="207" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>132</v>
       </c>
@@ -10763,11 +11798,17 @@
       <c r="I207" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="L207" s="3"/>
+      <c r="J207" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M207" s="3"/>
       <c r="N207" s="3"/>
-    </row>
-    <row r="208" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O207" s="3"/>
+    </row>
+    <row r="208" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>133</v>
       </c>
@@ -10799,13 +11840,16 @@
         <v>867</v>
       </c>
       <c r="K208" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L208" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L208" s="3"/>
       <c r="M208" s="3"/>
       <c r="N208" s="3"/>
-    </row>
-    <row r="209" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O208" s="3"/>
+    </row>
+    <row r="209" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>133</v>
       </c>
@@ -10833,11 +11877,17 @@
       <c r="I209" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="L209" s="3"/>
+      <c r="J209" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M209" s="3"/>
       <c r="N209" s="3"/>
-    </row>
-    <row r="210" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O209" s="3"/>
+    </row>
+    <row r="210" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>133</v>
       </c>
@@ -10865,11 +11915,17 @@
       <c r="I210" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="L210" s="3"/>
+      <c r="J210" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M210" s="3"/>
       <c r="N210" s="3"/>
-    </row>
-    <row r="211" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O210" s="3"/>
+    </row>
+    <row r="211" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>133</v>
       </c>
@@ -10897,11 +11953,17 @@
       <c r="I211" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="L211" s="3"/>
+      <c r="J211" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M211" s="3"/>
       <c r="N211" s="3"/>
-    </row>
-    <row r="212" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O211" s="3"/>
+    </row>
+    <row r="212" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>133</v>
       </c>
@@ -10929,11 +11991,17 @@
       <c r="I212" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="L212" s="3"/>
+      <c r="J212" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M212" s="3"/>
       <c r="N212" s="3"/>
-    </row>
-    <row r="213" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O212" s="3"/>
+    </row>
+    <row r="213" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>133</v>
       </c>
@@ -10961,11 +12029,17 @@
       <c r="I213" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="L213" s="3"/>
+      <c r="J213" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M213" s="3"/>
       <c r="N213" s="3"/>
-    </row>
-    <row r="214" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O213" s="3"/>
+    </row>
+    <row r="214" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>133</v>
       </c>
@@ -10993,11 +12067,17 @@
       <c r="I214" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="L214" s="3"/>
+      <c r="J214" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M214" s="3"/>
       <c r="N214" s="3"/>
-    </row>
-    <row r="215" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O214" s="3"/>
+    </row>
+    <row r="215" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>133</v>
       </c>
@@ -11025,11 +12105,17 @@
       <c r="I215" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="L215" s="3"/>
+      <c r="J215" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K215" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M215" s="3"/>
       <c r="N215" s="3"/>
-    </row>
-    <row r="216" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O215" s="3"/>
+    </row>
+    <row r="216" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>133</v>
       </c>
@@ -11057,11 +12143,17 @@
       <c r="I216" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="L216" s="3"/>
+      <c r="J216" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M216" s="3"/>
       <c r="N216" s="3"/>
-    </row>
-    <row r="217" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O216" s="3"/>
+    </row>
+    <row r="217" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>134</v>
       </c>
@@ -11089,11 +12181,17 @@
       <c r="I217" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="L217" s="3"/>
+      <c r="J217" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M217" s="3"/>
       <c r="N217" s="3"/>
-    </row>
-    <row r="218" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O217" s="3"/>
+    </row>
+    <row r="218" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>134</v>
       </c>
@@ -11121,11 +12219,17 @@
       <c r="I218" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="L218" s="3"/>
+      <c r="J218" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K218" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M218" s="3"/>
       <c r="N218" s="3"/>
-    </row>
-    <row r="219" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O218" s="3"/>
+    </row>
+    <row r="219" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>134</v>
       </c>
@@ -11153,11 +12257,17 @@
       <c r="I219" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="L219" s="3"/>
+      <c r="J219" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M219" s="3"/>
       <c r="N219" s="3"/>
-    </row>
-    <row r="220" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O219" s="3"/>
+    </row>
+    <row r="220" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>134</v>
       </c>
@@ -11185,11 +12295,17 @@
       <c r="I220" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="L220" s="3"/>
+      <c r="J220" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M220" s="3"/>
       <c r="N220" s="3"/>
-    </row>
-    <row r="221" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O220" s="3"/>
+    </row>
+    <row r="221" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>134</v>
       </c>
@@ -11217,11 +12333,17 @@
       <c r="I221" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="L221" s="3"/>
+      <c r="J221" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M221" s="3"/>
       <c r="N221" s="3"/>
-    </row>
-    <row r="222" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O221" s="3"/>
+    </row>
+    <row r="222" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>134</v>
       </c>
@@ -11249,11 +12371,17 @@
       <c r="I222" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="L222" s="3"/>
+      <c r="J222" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K222" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M222" s="3"/>
       <c r="N222" s="3"/>
-    </row>
-    <row r="223" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O222" s="3"/>
+    </row>
+    <row r="223" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>134</v>
       </c>
@@ -11281,11 +12409,17 @@
       <c r="I223" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="L223" s="3"/>
+      <c r="J223" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M223" s="3"/>
       <c r="N223" s="3"/>
-    </row>
-    <row r="224" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O223" s="3"/>
+    </row>
+    <row r="224" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>134</v>
       </c>
@@ -11313,11 +12447,17 @@
       <c r="I224" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="L224" s="3"/>
+      <c r="J224" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M224" s="3"/>
       <c r="N224" s="3"/>
-    </row>
-    <row r="225" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O224" s="3"/>
+    </row>
+    <row r="225" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>134</v>
       </c>
@@ -11345,11 +12485,17 @@
       <c r="I225" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="L225" s="3"/>
+      <c r="J225" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M225" s="3"/>
       <c r="N225" s="3"/>
-    </row>
-    <row r="226" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O225" s="3"/>
+    </row>
+    <row r="226" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>134</v>
       </c>
@@ -11377,11 +12523,17 @@
       <c r="I226" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="L226" s="3"/>
+      <c r="J226" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K226" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M226" s="3"/>
       <c r="N226" s="3"/>
-    </row>
-    <row r="227" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O226" s="3"/>
+    </row>
+    <row r="227" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>134</v>
       </c>
@@ -11409,11 +12561,17 @@
       <c r="I227" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="L227" s="3"/>
+      <c r="J227" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K227" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M227" s="3"/>
       <c r="N227" s="3"/>
-    </row>
-    <row r="228" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O227" s="3"/>
+    </row>
+    <row r="228" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>134</v>
       </c>
@@ -11441,11 +12599,17 @@
       <c r="I228" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="L228" s="3"/>
+      <c r="J228" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K228" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M228" s="3"/>
       <c r="N228" s="3"/>
-    </row>
-    <row r="229" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O228" s="3"/>
+    </row>
+    <row r="229" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>135</v>
       </c>
@@ -11473,11 +12637,17 @@
       <c r="I229" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="L229" s="3"/>
+      <c r="J229" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K229" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M229" s="3"/>
       <c r="N229" s="3"/>
-    </row>
-    <row r="230" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O229" s="3"/>
+    </row>
+    <row r="230" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>135</v>
       </c>
@@ -11505,11 +12675,17 @@
       <c r="I230" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="L230" s="3"/>
+      <c r="J230" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M230" s="3"/>
       <c r="N230" s="3"/>
-    </row>
-    <row r="231" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O230" s="3"/>
+    </row>
+    <row r="231" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>135</v>
       </c>
@@ -11537,11 +12713,17 @@
       <c r="I231" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="L231" s="3"/>
+      <c r="J231" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M231" s="3"/>
       <c r="N231" s="3"/>
-    </row>
-    <row r="232" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O231" s="3"/>
+    </row>
+    <row r="232" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>135</v>
       </c>
@@ -11569,11 +12751,17 @@
       <c r="I232" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="L232" s="3"/>
+      <c r="J232" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M232" s="3"/>
       <c r="N232" s="3"/>
-    </row>
-    <row r="233" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O232" s="3"/>
+    </row>
+    <row r="233" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>135</v>
       </c>
@@ -11601,11 +12789,17 @@
       <c r="I233" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="L233" s="3"/>
+      <c r="J233" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K233" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M233" s="3"/>
       <c r="N233" s="3"/>
-    </row>
-    <row r="234" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O233" s="3"/>
+    </row>
+    <row r="234" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>135</v>
       </c>
@@ -11633,11 +12827,17 @@
       <c r="I234" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="L234" s="3"/>
+      <c r="J234" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M234" s="3"/>
       <c r="N234" s="3"/>
-    </row>
-    <row r="235" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O234" s="3"/>
+    </row>
+    <row r="235" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>135</v>
       </c>
@@ -11665,11 +12865,17 @@
       <c r="I235" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="L235" s="3"/>
+      <c r="J235" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K235" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M235" s="3"/>
       <c r="N235" s="3"/>
-    </row>
-    <row r="236" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O235" s="3"/>
+    </row>
+    <row r="236" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>136</v>
       </c>
@@ -11697,11 +12903,17 @@
       <c r="I236" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L236" s="3"/>
+      <c r="J236" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M236" s="3"/>
       <c r="N236" s="3"/>
-    </row>
-    <row r="237" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O236" s="3"/>
+    </row>
+    <row r="237" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>136</v>
       </c>
@@ -11729,11 +12941,17 @@
       <c r="I237" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="L237" s="3"/>
+      <c r="J237" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K237" s="2" t="s">
+        <v>894</v>
+      </c>
       <c r="M237" s="3"/>
       <c r="N237" s="3"/>
-    </row>
-    <row r="238" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O237" s="3"/>
+    </row>
+    <row r="238" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>137</v>
       </c>
@@ -11761,11 +12979,17 @@
       <c r="I238" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L238" s="3"/>
+      <c r="J238" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K238" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M238" s="3"/>
       <c r="N238" s="3"/>
-    </row>
-    <row r="239" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O238" s="3"/>
+    </row>
+    <row r="239" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>137</v>
       </c>
@@ -11793,11 +13017,17 @@
       <c r="I239" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L239" s="3"/>
+      <c r="J239" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K239" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M239" s="3"/>
       <c r="N239" s="3"/>
-    </row>
-    <row r="240" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O239" s="3"/>
+    </row>
+    <row r="240" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>137</v>
       </c>
@@ -11825,11 +13055,17 @@
       <c r="I240" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L240" s="3"/>
+      <c r="J240" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K240" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M240" s="3"/>
       <c r="N240" s="3"/>
-    </row>
-    <row r="241" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O240" s="3"/>
+    </row>
+    <row r="241" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>137</v>
       </c>
@@ -11857,11 +13093,17 @@
       <c r="I241" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L241" s="3"/>
+      <c r="J241" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M241" s="3"/>
       <c r="N241" s="3"/>
-    </row>
-    <row r="242" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O241" s="3"/>
+    </row>
+    <row r="242" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>137</v>
       </c>
@@ -11889,11 +13131,17 @@
       <c r="I242" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="L242" s="3"/>
+      <c r="J242" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K242" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M242" s="3"/>
       <c r="N242" s="3"/>
-    </row>
-    <row r="243" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O242" s="3"/>
+    </row>
+    <row r="243" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>137</v>
       </c>
@@ -11921,11 +13169,17 @@
       <c r="I243" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="L243" s="3"/>
+      <c r="J243" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K243" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M243" s="3"/>
       <c r="N243" s="3"/>
-    </row>
-    <row r="244" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O243" s="3"/>
+    </row>
+    <row r="244" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>137</v>
       </c>
@@ -11953,17 +13207,23 @@
       <c r="I244" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="L244" s="3" t="s">
+      <c r="J244" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M244" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M244" s="3" t="s">
+      <c r="N244" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="N244" s="3" t="s">
+      <c r="O244" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="245" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>137</v>
       </c>
@@ -11991,17 +13251,23 @@
       <c r="I245" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="L245" s="3" t="s">
+      <c r="J245" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K245" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M245" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M245" s="3" t="s">
+      <c r="N245" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="N245" s="3" t="s">
+      <c r="O245" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="246" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>137</v>
       </c>
@@ -12029,17 +13295,23 @@
       <c r="I246" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="L246" s="3" t="s">
+      <c r="J246" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K246" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M246" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M246" s="3" t="s">
+      <c r="N246" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="N246" s="3" t="s">
+      <c r="O246" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="247" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>138</v>
       </c>
@@ -12067,11 +13339,17 @@
       <c r="I247" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="L247" s="3"/>
+      <c r="J247" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="K247" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M247" s="3"/>
       <c r="N247" s="3"/>
-    </row>
-    <row r="248" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O247" s="3"/>
+    </row>
+    <row r="248" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>138</v>
       </c>
@@ -12099,11 +13377,17 @@
       <c r="I248" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="L248" s="3"/>
+      <c r="J248" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K248" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M248" s="3"/>
       <c r="N248" s="3"/>
-    </row>
-    <row r="249" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O248" s="3"/>
+    </row>
+    <row r="249" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>138</v>
       </c>
@@ -12131,11 +13415,17 @@
       <c r="I249" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="L249" s="3"/>
+      <c r="J249" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="K249" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M249" s="3"/>
       <c r="N249" s="3"/>
-    </row>
-    <row r="250" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O249" s="3"/>
+    </row>
+    <row r="250" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>138</v>
       </c>
@@ -12163,8 +13453,11 @@
       <c r="I250" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="L250" s="3" t="s">
-        <v>91</v>
+      <c r="J250" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K250" s="2" t="s">
+        <v>881</v>
       </c>
       <c r="M250" s="3" t="s">
         <v>91</v>
@@ -12172,8 +13465,11 @@
       <c r="N250" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O250" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>139</v>
       </c>
@@ -12201,11 +13497,17 @@
       <c r="I251" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="L251" s="3"/>
+      <c r="J251" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K251" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M251" s="3"/>
       <c r="N251" s="3"/>
-    </row>
-    <row r="252" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O251" s="3"/>
+    </row>
+    <row r="252" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>140</v>
       </c>
@@ -12233,11 +13535,17 @@
       <c r="I252" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L252" s="3"/>
+      <c r="J252" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K252" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M252" s="3"/>
       <c r="N252" s="3"/>
-    </row>
-    <row r="253" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O252" s="3"/>
+    </row>
+    <row r="253" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>140</v>
       </c>
@@ -12265,11 +13573,17 @@
       <c r="I253" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L253" s="3"/>
+      <c r="J253" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K253" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M253" s="3"/>
       <c r="N253" s="3"/>
-    </row>
-    <row r="254" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O253" s="3"/>
+    </row>
+    <row r="254" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>140</v>
       </c>
@@ -12297,11 +13611,17 @@
       <c r="I254" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L254" s="3"/>
+      <c r="J254" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K254" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M254" s="3"/>
       <c r="N254" s="3"/>
-    </row>
-    <row r="255" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O254" s="3"/>
+    </row>
+    <row r="255" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>140</v>
       </c>
@@ -12329,11 +13649,17 @@
       <c r="I255" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L255" s="3"/>
+      <c r="J255" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K255" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M255" s="3"/>
       <c r="N255" s="3"/>
-    </row>
-    <row r="256" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O255" s="3"/>
+    </row>
+    <row r="256" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>140</v>
       </c>
@@ -12361,11 +13687,17 @@
       <c r="I256" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="L256" s="3"/>
+      <c r="J256" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K256" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
-    </row>
-    <row r="257" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O256" s="3"/>
+    </row>
+    <row r="257" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>140</v>
       </c>
@@ -12393,17 +13725,23 @@
       <c r="I257" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L257" s="3" t="s">
+      <c r="J257" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K257" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M257" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M257" s="3">
+      <c r="N257" s="3">
         <v>0</v>
       </c>
-      <c r="N257" s="3" t="s">
+      <c r="O257" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="258" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>140</v>
       </c>
@@ -12431,17 +13769,23 @@
       <c r="I258" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L258" s="3" t="s">
+      <c r="J258" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K258" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M258" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M258" s="3">
+      <c r="N258" s="3">
         <v>25</v>
       </c>
-      <c r="N258" s="3" t="s">
+      <c r="O258" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="259" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>140</v>
       </c>
@@ -12469,17 +13813,23 @@
       <c r="I259" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L259" s="3" t="s">
+      <c r="J259" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K259" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M259" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M259" s="3">
+      <c r="N259" s="3">
         <v>45</v>
       </c>
-      <c r="N259" s="3" t="s">
+      <c r="O259" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="260" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>140</v>
       </c>
@@ -12507,17 +13857,23 @@
       <c r="I260" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L260" s="3" t="s">
+      <c r="J260" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K260" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M260" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M260" s="3">
+      <c r="N260" s="3">
         <v>70</v>
       </c>
-      <c r="N260" s="3" t="s">
+      <c r="O260" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="261" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>140</v>
       </c>
@@ -12545,17 +13901,23 @@
       <c r="I261" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L261" s="3" t="s">
+      <c r="J261" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K261" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M261" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="M261" s="3">
+      <c r="N261" s="3">
         <v>0</v>
       </c>
-      <c r="N261" s="3" t="s">
+      <c r="O261" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="262" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>140</v>
       </c>
@@ -12583,17 +13945,23 @@
       <c r="I262" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L262" s="3" t="s">
+      <c r="J262" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K262" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M262" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="M262" s="3">
+      <c r="N262" s="3">
         <v>15</v>
       </c>
-      <c r="N262" s="3" t="s">
+      <c r="O262" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="263" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>140</v>
       </c>
@@ -12621,17 +13989,23 @@
       <c r="I263" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L263" s="3" t="s">
+      <c r="J263" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K263" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M263" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="M263" s="3">
+      <c r="N263" s="3">
         <v>30</v>
       </c>
-      <c r="N263" s="3" t="s">
+      <c r="O263" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="264" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>140</v>
       </c>
@@ -12659,17 +14033,23 @@
       <c r="I264" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="L264" s="3" t="s">
+      <c r="J264" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K264" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="M264" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="M264" s="3">
+      <c r="N264" s="3">
         <v>50</v>
       </c>
-      <c r="N264" s="3" t="s">
+      <c r="O264" s="3" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="265" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>141</v>
       </c>
@@ -12679,11 +14059,11 @@
       <c r="C265" s="1">
         <v>14101</v>
       </c>
-      <c r="L265" s="6"/>
       <c r="M265" s="6"/>
       <c r="N265" s="6"/>
-    </row>
-    <row r="266" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O265" s="6"/>
+    </row>
+    <row r="266" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>142</v>
       </c>
@@ -12711,11 +14091,17 @@
       <c r="I266" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="L266" s="3"/>
+      <c r="J266" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K266" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M266" s="3"/>
       <c r="N266" s="3"/>
-    </row>
-    <row r="267" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O266" s="3"/>
+    </row>
+    <row r="267" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>142</v>
       </c>
@@ -12743,11 +14129,17 @@
       <c r="I267" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="L267" s="3"/>
+      <c r="J267" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K267" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M267" s="3"/>
       <c r="N267" s="3"/>
-    </row>
-    <row r="268" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O267" s="3"/>
+    </row>
+    <row r="268" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>142</v>
       </c>
@@ -12775,11 +14167,17 @@
       <c r="I268" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="L268" s="3"/>
+      <c r="J268" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K268" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M268" s="3"/>
       <c r="N268" s="3"/>
-    </row>
-    <row r="269" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O268" s="3"/>
+    </row>
+    <row r="269" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>142</v>
       </c>
@@ -12807,11 +14205,17 @@
       <c r="I269" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="L269" s="3"/>
+      <c r="J269" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K269" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M269" s="3"/>
       <c r="N269" s="3"/>
-    </row>
-    <row r="270" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O269" s="3"/>
+    </row>
+    <row r="270" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>142</v>
       </c>
@@ -12839,11 +14243,17 @@
       <c r="I270" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="L270" s="3"/>
+      <c r="J270" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K270" s="2" t="s">
+        <v>897</v>
+      </c>
       <c r="M270" s="3"/>
       <c r="N270" s="3"/>
-    </row>
-    <row r="271" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O270" s="3"/>
+    </row>
+    <row r="271" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>142</v>
       </c>
@@ -12871,11 +14281,17 @@
       <c r="I271" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="L271" s="3"/>
+      <c r="J271" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K271" s="2" t="s">
+        <v>897</v>
+      </c>
       <c r="M271" s="3"/>
       <c r="N271" s="3"/>
-    </row>
-    <row r="272" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O271" s="3"/>
+    </row>
+    <row r="272" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>142</v>
       </c>
@@ -12903,11 +14319,17 @@
       <c r="I272" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="L272" s="3"/>
+      <c r="J272" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K272" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M272" s="3"/>
       <c r="N272" s="3"/>
-    </row>
-    <row r="273" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O272" s="3"/>
+    </row>
+    <row r="273" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>142</v>
       </c>
@@ -12935,11 +14357,17 @@
       <c r="I273" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L273" s="3"/>
+      <c r="J273" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K273" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M273" s="3"/>
       <c r="N273" s="3"/>
-    </row>
-    <row r="274" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O273" s="3"/>
+    </row>
+    <row r="274" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>142</v>
       </c>
@@ -12967,11 +14395,17 @@
       <c r="I274" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L274" s="3"/>
+      <c r="J274" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K274" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M274" s="3"/>
       <c r="N274" s="3"/>
-    </row>
-    <row r="275" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O274" s="3"/>
+    </row>
+    <row r="275" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>142</v>
       </c>
@@ -12999,11 +14433,17 @@
       <c r="I275" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L275" s="3"/>
+      <c r="J275" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K275" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M275" s="3"/>
       <c r="N275" s="3"/>
-    </row>
-    <row r="276" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O275" s="3"/>
+    </row>
+    <row r="276" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>142</v>
       </c>
@@ -13031,11 +14471,17 @@
       <c r="I276" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L276" s="3"/>
+      <c r="J276" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K276" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M276" s="3"/>
       <c r="N276" s="3"/>
-    </row>
-    <row r="277" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O276" s="3"/>
+    </row>
+    <row r="277" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>142</v>
       </c>
@@ -13063,11 +14509,17 @@
       <c r="I277" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L277" s="3"/>
+      <c r="J277" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K277" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M277" s="3"/>
       <c r="N277" s="3"/>
-    </row>
-    <row r="278" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O277" s="3"/>
+    </row>
+    <row r="278" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>142</v>
       </c>
@@ -13095,11 +14547,17 @@
       <c r="I278" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L278" s="3"/>
+      <c r="J278" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K278" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M278" s="3"/>
       <c r="N278" s="3"/>
-    </row>
-    <row r="279" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O278" s="3"/>
+    </row>
+    <row r="279" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>142</v>
       </c>
@@ -13127,11 +14585,17 @@
       <c r="I279" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L279" s="3"/>
+      <c r="J279" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K279" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M279" s="3"/>
       <c r="N279" s="3"/>
-    </row>
-    <row r="280" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O279" s="3"/>
+    </row>
+    <row r="280" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>142</v>
       </c>
@@ -13159,11 +14623,17 @@
       <c r="I280" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L280" s="3"/>
+      <c r="J280" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K280" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M280" s="3"/>
       <c r="N280" s="3"/>
-    </row>
-    <row r="281" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O280" s="3"/>
+    </row>
+    <row r="281" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>142</v>
       </c>
@@ -13191,11 +14661,17 @@
       <c r="I281" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L281" s="3"/>
+      <c r="J281" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K281" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M281" s="3"/>
       <c r="N281" s="3"/>
-    </row>
-    <row r="282" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O281" s="3"/>
+    </row>
+    <row r="282" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>142</v>
       </c>
@@ -13223,11 +14699,17 @@
       <c r="I282" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L282" s="3"/>
+      <c r="J282" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K282" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M282" s="3"/>
       <c r="N282" s="3"/>
-    </row>
-    <row r="283" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O282" s="3"/>
+    </row>
+    <row r="283" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>142</v>
       </c>
@@ -13255,11 +14737,17 @@
       <c r="I283" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L283" s="3"/>
+      <c r="J283" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K283" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M283" s="3"/>
       <c r="N283" s="3"/>
-    </row>
-    <row r="284" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O283" s="3"/>
+    </row>
+    <row r="284" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>142</v>
       </c>
@@ -13287,11 +14775,17 @@
       <c r="I284" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L284" s="3"/>
+      <c r="J284" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K284" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M284" s="3"/>
       <c r="N284" s="3"/>
-    </row>
-    <row r="285" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O284" s="3"/>
+    </row>
+    <row r="285" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>142</v>
       </c>
@@ -13319,11 +14813,17 @@
       <c r="I285" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L285" s="3"/>
+      <c r="J285" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K285" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M285" s="3"/>
       <c r="N285" s="3"/>
-    </row>
-    <row r="286" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O285" s="3"/>
+    </row>
+    <row r="286" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>142</v>
       </c>
@@ -13351,11 +14851,17 @@
       <c r="I286" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L286" s="3"/>
+      <c r="J286" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K286" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M286" s="3"/>
       <c r="N286" s="3"/>
-    </row>
-    <row r="287" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O286" s="3"/>
+    </row>
+    <row r="287" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>142</v>
       </c>
@@ -13383,11 +14889,17 @@
       <c r="I287" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L287" s="3"/>
+      <c r="J287" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K287" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M287" s="3"/>
       <c r="N287" s="3"/>
-    </row>
-    <row r="288" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O287" s="3"/>
+    </row>
+    <row r="288" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>142</v>
       </c>
@@ -13415,11 +14927,17 @@
       <c r="I288" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L288" s="3"/>
+      <c r="J288" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K288" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M288" s="3"/>
       <c r="N288" s="3"/>
-    </row>
-    <row r="289" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O288" s="3"/>
+    </row>
+    <row r="289" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>142</v>
       </c>
@@ -13447,11 +14965,17 @@
       <c r="I289" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="L289" s="3"/>
+      <c r="J289" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K289" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M289" s="3"/>
       <c r="N289" s="3"/>
-    </row>
-    <row r="290" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O289" s="3"/>
+    </row>
+    <row r="290" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>142</v>
       </c>
@@ -13479,11 +15003,17 @@
       <c r="I290" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="L290" s="3"/>
+      <c r="J290" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K290" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M290" s="3"/>
       <c r="N290" s="3"/>
-    </row>
-    <row r="291" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O290" s="3"/>
+    </row>
+    <row r="291" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>142</v>
       </c>
@@ -13511,11 +15041,17 @@
       <c r="I291" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="L291" s="3"/>
+      <c r="J291" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K291" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M291" s="3"/>
       <c r="N291" s="3"/>
-    </row>
-    <row r="292" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O291" s="3"/>
+    </row>
+    <row r="292" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>142</v>
       </c>
@@ -13543,11 +15079,17 @@
       <c r="I292" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="L292" s="3"/>
+      <c r="J292" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K292" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M292" s="3"/>
       <c r="N292" s="3"/>
-    </row>
-    <row r="293" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O292" s="3"/>
+    </row>
+    <row r="293" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>142</v>
       </c>
@@ -13575,11 +15117,17 @@
       <c r="I293" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="L293" s="3"/>
+      <c r="J293" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K293" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M293" s="3"/>
       <c r="N293" s="3"/>
-    </row>
-    <row r="294" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O293" s="3"/>
+    </row>
+    <row r="294" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>142</v>
       </c>
@@ -13607,11 +15155,17 @@
       <c r="I294" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="L294" s="3"/>
+      <c r="J294" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K294" s="2" t="s">
+        <v>897</v>
+      </c>
       <c r="M294" s="3"/>
       <c r="N294" s="3"/>
-    </row>
-    <row r="295" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O294" s="3"/>
+    </row>
+    <row r="295" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>143</v>
       </c>
@@ -13639,11 +15193,17 @@
       <c r="I295" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="L295" s="3"/>
+      <c r="J295" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K295" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M295" s="3"/>
       <c r="N295" s="3"/>
-    </row>
-    <row r="296" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O295" s="3"/>
+    </row>
+    <row r="296" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>143</v>
       </c>
@@ -13671,11 +15231,17 @@
       <c r="I296" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="L296" s="3"/>
+      <c r="J296" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K296" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M296" s="3"/>
       <c r="N296" s="3"/>
-    </row>
-    <row r="297" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O296" s="3"/>
+    </row>
+    <row r="297" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>143</v>
       </c>
@@ -13703,11 +15269,17 @@
       <c r="I297" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="L297" s="3"/>
+      <c r="J297" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K297" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M297" s="3"/>
       <c r="N297" s="3"/>
-    </row>
-    <row r="298" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O297" s="3"/>
+    </row>
+    <row r="298" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>143</v>
       </c>
@@ -13735,11 +15307,17 @@
       <c r="I298" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="L298" s="3"/>
+      <c r="J298" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K298" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M298" s="3"/>
       <c r="N298" s="3"/>
-    </row>
-    <row r="299" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O298" s="3"/>
+    </row>
+    <row r="299" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>143</v>
       </c>
@@ -13767,11 +15345,17 @@
       <c r="I299" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="L299" s="3"/>
+      <c r="J299" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K299" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M299" s="3"/>
       <c r="N299" s="3"/>
-    </row>
-    <row r="300" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O299" s="3"/>
+    </row>
+    <row r="300" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>144</v>
       </c>
@@ -13799,11 +15383,17 @@
       <c r="I300" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="L300" s="3"/>
+      <c r="J300" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K300" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M300" s="3"/>
       <c r="N300" s="3"/>
-    </row>
-    <row r="301" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O300" s="3"/>
+    </row>
+    <row r="301" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>144</v>
       </c>
@@ -13831,14 +15421,20 @@
       <c r="I301" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J301" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K301" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L301" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L301" s="3"/>
       <c r="M301" s="3"/>
       <c r="N301" s="3"/>
-    </row>
-    <row r="302" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O301" s="3"/>
+    </row>
+    <row r="302" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>144</v>
       </c>
@@ -13866,11 +15462,17 @@
       <c r="I302" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="L302" s="3"/>
+      <c r="J302" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="K302" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="M302" s="3"/>
       <c r="N302" s="3"/>
-    </row>
-    <row r="303" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O302" s="3"/>
+    </row>
+    <row r="303" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>144</v>
       </c>
@@ -13898,11 +15500,17 @@
       <c r="I303" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="L303" s="3"/>
+      <c r="J303" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K303" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M303" s="3"/>
       <c r="N303" s="3"/>
-    </row>
-    <row r="304" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O303" s="3"/>
+    </row>
+    <row r="304" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>144</v>
       </c>
@@ -13930,11 +15538,17 @@
       <c r="I304" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="L304" s="3"/>
+      <c r="J304" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K304" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M304" s="3"/>
       <c r="N304" s="3"/>
-    </row>
-    <row r="305" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O304" s="3"/>
+    </row>
+    <row r="305" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>144</v>
       </c>
@@ -13962,11 +15576,17 @@
       <c r="I305" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="L305" s="3"/>
+      <c r="J305" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K305" s="2" t="s">
+        <v>881</v>
+      </c>
       <c r="M305" s="3"/>
       <c r="N305" s="3"/>
-    </row>
-    <row r="306" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O305" s="3"/>
+    </row>
+    <row r="306" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>145</v>
       </c>
@@ -13994,14 +15614,20 @@
       <c r="I306" s="2" t="s">
         <v>727</v>
       </c>
+      <c r="J306" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K306" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="L306" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L306" s="3"/>
       <c r="M306" s="3"/>
       <c r="N306" s="3"/>
-    </row>
-    <row r="307" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O306" s="3"/>
+    </row>
+    <row r="307" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>145</v>
       </c>
@@ -14029,11 +15655,17 @@
       <c r="I307" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="L307" s="3"/>
+      <c r="J307" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K307" s="2" t="s">
+        <v>897</v>
+      </c>
       <c r="M307" s="3"/>
       <c r="N307" s="3"/>
-    </row>
-    <row r="308" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O307" s="3"/>
+    </row>
+    <row r="308" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>145</v>
       </c>
@@ -14061,11 +15693,17 @@
       <c r="I308" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="L308" s="3"/>
+      <c r="J308" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K308" s="2" t="s">
+        <v>897</v>
+      </c>
       <c r="M308" s="3"/>
       <c r="N308" s="3"/>
-    </row>
-    <row r="309" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O308" s="3"/>
+    </row>
+    <row r="309" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>145</v>
       </c>
@@ -14093,14 +15731,20 @@
       <c r="I309" s="2" t="s">
         <v>728</v>
       </c>
+      <c r="J309" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K309" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="L309" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L309" s="3"/>
       <c r="M309" s="3"/>
       <c r="N309" s="3"/>
-    </row>
-    <row r="310" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O309" s="3"/>
+    </row>
+    <row r="310" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>145</v>
       </c>
@@ -14128,14 +15772,20 @@
       <c r="I310" s="2" t="s">
         <v>729</v>
       </c>
+      <c r="J310" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K310" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="L310" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L310" s="3"/>
       <c r="M310" s="3"/>
       <c r="N310" s="3"/>
-    </row>
-    <row r="311" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O310" s="3"/>
+    </row>
+    <row r="311" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>145</v>
       </c>
@@ -14163,14 +15813,20 @@
       <c r="I311" s="2" t="s">
         <v>730</v>
       </c>
+      <c r="J311" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K311" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="L311" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="L311" s="3"/>
       <c r="M311" s="3"/>
       <c r="N311" s="3"/>
-    </row>
-    <row r="312" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O311" s="3"/>
+    </row>
+    <row r="312" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>146</v>
       </c>
@@ -14198,11 +15854,17 @@
       <c r="I312" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="L312" s="3"/>
+      <c r="J312" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M312" s="3"/>
       <c r="N312" s="3"/>
-    </row>
-    <row r="313" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O312" s="3"/>
+    </row>
+    <row r="313" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>146</v>
       </c>
@@ -14230,11 +15892,17 @@
       <c r="I313" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="L313" s="3"/>
+      <c r="J313" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K313" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M313" s="3"/>
       <c r="N313" s="3"/>
-    </row>
-    <row r="314" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O313" s="3"/>
+    </row>
+    <row r="314" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>146</v>
       </c>
@@ -14262,11 +15930,17 @@
       <c r="I314" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="L314" s="3"/>
+      <c r="J314" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K314" s="2" t="s">
+        <v>877</v>
+      </c>
       <c r="M314" s="3"/>
       <c r="N314" s="3"/>
-    </row>
-    <row r="315" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O314" s="3"/>
+    </row>
+    <row r="315" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>147</v>
       </c>
@@ -14294,11 +15968,17 @@
       <c r="I315" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="L315" s="3"/>
+      <c r="J315" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K315" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M315" s="3"/>
       <c r="N315" s="3"/>
-    </row>
-    <row r="316" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O315" s="3"/>
+    </row>
+    <row r="316" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>147</v>
       </c>
@@ -14326,11 +16006,17 @@
       <c r="I316" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="L316" s="3"/>
+      <c r="J316" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K316" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M316" s="3"/>
       <c r="N316" s="3"/>
-    </row>
-    <row r="317" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O316" s="3"/>
+    </row>
+    <row r="317" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>147</v>
       </c>
@@ -14358,11 +16044,17 @@
       <c r="I317" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="L317" s="3"/>
+      <c r="J317" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K317" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M317" s="3"/>
       <c r="N317" s="3"/>
-    </row>
-    <row r="318" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O317" s="3"/>
+    </row>
+    <row r="318" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>147</v>
       </c>
@@ -14390,11 +16082,17 @@
       <c r="I318" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="L318" s="3"/>
+      <c r="J318" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M318" s="3"/>
       <c r="N318" s="3"/>
-    </row>
-    <row r="319" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O318" s="3"/>
+    </row>
+    <row r="319" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>148</v>
       </c>
@@ -14422,14 +16120,20 @@
       <c r="I319" s="2" t="s">
         <v>735</v>
       </c>
+      <c r="J319" s="2" t="s">
+        <v>879</v>
+      </c>
       <c r="K319" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="L319" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L319" s="3"/>
       <c r="M319" s="3"/>
       <c r="N319" s="3"/>
-    </row>
-    <row r="320" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O319" s="3"/>
+    </row>
+    <row r="320" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>148</v>
       </c>
@@ -14457,14 +16161,20 @@
       <c r="I320" s="2" t="s">
         <v>735</v>
       </c>
+      <c r="J320" s="2" t="s">
+        <v>898</v>
+      </c>
       <c r="K320" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L320" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L320" s="3"/>
       <c r="M320" s="3"/>
       <c r="N320" s="3"/>
-    </row>
-    <row r="321" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O320" s="3"/>
+    </row>
+    <row r="321" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>148</v>
       </c>
@@ -14492,14 +16202,20 @@
       <c r="I321" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J321" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K321" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L321" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L321" s="3"/>
       <c r="M321" s="3"/>
       <c r="N321" s="3"/>
-    </row>
-    <row r="322" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O321" s="3"/>
+    </row>
+    <row r="322" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>148</v>
       </c>
@@ -14527,11 +16243,17 @@
       <c r="I322" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="L322" s="3"/>
+      <c r="J322" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K322" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M322" s="3"/>
       <c r="N322" s="3"/>
-    </row>
-    <row r="323" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O322" s="3"/>
+    </row>
+    <row r="323" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>148</v>
       </c>
@@ -14559,11 +16281,17 @@
       <c r="I323" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="L323" s="3"/>
+      <c r="J323" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K323" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M323" s="3"/>
       <c r="N323" s="3"/>
-    </row>
-    <row r="324" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O323" s="3"/>
+    </row>
+    <row r="324" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>148</v>
       </c>
@@ -14591,11 +16319,17 @@
       <c r="I324" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="L324" s="3"/>
+      <c r="J324" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K324" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M324" s="3"/>
       <c r="N324" s="3"/>
-    </row>
-    <row r="325" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O324" s="3"/>
+    </row>
+    <row r="325" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>149</v>
       </c>
@@ -14623,14 +16357,20 @@
       <c r="I325" s="2" t="s">
         <v>652</v>
       </c>
+      <c r="J325" s="2" t="s">
+        <v>872</v>
+      </c>
       <c r="K325" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L325" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="L325" s="3"/>
       <c r="M325" s="3"/>
       <c r="N325" s="3"/>
-    </row>
-    <row r="326" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O325" s="3"/>
+    </row>
+    <row r="326" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>149</v>
       </c>
@@ -14658,11 +16398,17 @@
       <c r="I326" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L326" s="3"/>
+      <c r="J326" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K326" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M326" s="3"/>
       <c r="N326" s="3"/>
-    </row>
-    <row r="327" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O326" s="3"/>
+    </row>
+    <row r="327" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>149</v>
       </c>
@@ -14690,11 +16436,17 @@
       <c r="I327" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L327" s="3"/>
+      <c r="J327" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K327" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M327" s="3"/>
       <c r="N327" s="3"/>
-    </row>
-    <row r="328" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O327" s="3"/>
+    </row>
+    <row r="328" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>149</v>
       </c>
@@ -14722,11 +16474,17 @@
       <c r="I328" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L328" s="3"/>
+      <c r="J328" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K328" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M328" s="3"/>
       <c r="N328" s="3"/>
-    </row>
-    <row r="329" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O328" s="3"/>
+    </row>
+    <row r="329" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>149</v>
       </c>
@@ -14754,11 +16512,17 @@
       <c r="I329" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L329" s="3"/>
+      <c r="J329" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K329" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M329" s="3"/>
       <c r="N329" s="3"/>
-    </row>
-    <row r="330" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O329" s="3"/>
+    </row>
+    <row r="330" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>149</v>
       </c>
@@ -14786,11 +16550,17 @@
       <c r="I330" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L330" s="3"/>
+      <c r="J330" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K330" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M330" s="3"/>
       <c r="N330" s="3"/>
-    </row>
-    <row r="331" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O330" s="3"/>
+    </row>
+    <row r="331" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>149</v>
       </c>
@@ -14818,11 +16588,17 @@
       <c r="I331" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L331" s="3"/>
+      <c r="J331" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K331" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M331" s="3"/>
       <c r="N331" s="3"/>
-    </row>
-    <row r="332" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O331" s="3"/>
+    </row>
+    <row r="332" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>149</v>
       </c>
@@ -14850,11 +16626,17 @@
       <c r="I332" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L332" s="3"/>
+      <c r="J332" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K332" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M332" s="3"/>
       <c r="N332" s="3"/>
-    </row>
-    <row r="333" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O332" s="3"/>
+    </row>
+    <row r="333" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>149</v>
       </c>
@@ -14882,11 +16664,17 @@
       <c r="I333" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L333" s="3"/>
+      <c r="J333" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K333" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M333" s="3"/>
       <c r="N333" s="3"/>
-    </row>
-    <row r="334" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O333" s="3"/>
+    </row>
+    <row r="334" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>149</v>
       </c>
@@ -14914,11 +16702,17 @@
       <c r="I334" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L334" s="3"/>
+      <c r="J334" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K334" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M334" s="3"/>
       <c r="N334" s="3"/>
-    </row>
-    <row r="335" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O334" s="3"/>
+    </row>
+    <row r="335" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>149</v>
       </c>
@@ -14946,11 +16740,17 @@
       <c r="I335" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="L335" s="3"/>
+      <c r="J335" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K335" s="2" t="s">
+        <v>893</v>
+      </c>
       <c r="M335" s="3"/>
       <c r="N335" s="3"/>
-    </row>
-    <row r="336" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O335" s="3"/>
+    </row>
+    <row r="336" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>150</v>
       </c>
@@ -14978,11 +16778,17 @@
       <c r="I336" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="L336" s="3"/>
+      <c r="J336" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K336" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M336" s="3"/>
       <c r="N336" s="3"/>
-    </row>
-    <row r="337" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O336" s="3"/>
+    </row>
+    <row r="337" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>150</v>
       </c>
@@ -15010,11 +16816,17 @@
       <c r="I337" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="L337" s="3"/>
+      <c r="J337" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K337" s="2" t="s">
+        <v>886</v>
+      </c>
       <c r="M337" s="3"/>
       <c r="N337" s="3"/>
-    </row>
-    <row r="338" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O337" s="3"/>
+    </row>
+    <row r="338" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>151</v>
       </c>
@@ -15042,14 +16854,20 @@
       <c r="I338" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J338" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K338" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L338" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L338" s="3"/>
       <c r="M338" s="3"/>
       <c r="N338" s="3"/>
-    </row>
-    <row r="339" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O338" s="3"/>
+    </row>
+    <row r="339" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>151</v>
       </c>
@@ -15077,11 +16895,17 @@
       <c r="I339" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="L339" s="3"/>
+      <c r="J339" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K339" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M339" s="3"/>
       <c r="N339" s="3"/>
-    </row>
-    <row r="340" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O339" s="3"/>
+    </row>
+    <row r="340" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>152</v>
       </c>
@@ -15091,11 +16915,13 @@
       <c r="C340" s="1">
         <v>15201</v>
       </c>
-      <c r="L340" s="6"/>
+      <c r="J340" s="2"/>
+      <c r="K340" s="2"/>
       <c r="M340" s="6"/>
       <c r="N340" s="6"/>
-    </row>
-    <row r="341" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O340" s="6"/>
+    </row>
+    <row r="341" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>153</v>
       </c>
@@ -15123,14 +16949,20 @@
       <c r="I341" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J341" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K341" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L341" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L341" s="3"/>
       <c r="M341" s="3"/>
       <c r="N341" s="3"/>
-    </row>
-    <row r="342" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O341" s="3"/>
+    </row>
+    <row r="342" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>154</v>
       </c>
@@ -15158,11 +16990,17 @@
       <c r="I342" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="L342" s="3"/>
+      <c r="J342" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K342" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M342" s="3"/>
       <c r="N342" s="3"/>
-    </row>
-    <row r="343" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O342" s="3"/>
+    </row>
+    <row r="343" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>155</v>
       </c>
@@ -15190,14 +17028,20 @@
       <c r="I343" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J343" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K343" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L343" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L343" s="3"/>
       <c r="M343" s="3"/>
       <c r="N343" s="3"/>
-    </row>
-    <row r="344" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O343" s="3"/>
+    </row>
+    <row r="344" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>156</v>
       </c>
@@ -15225,14 +17069,20 @@
       <c r="I344" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J344" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K344" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L344" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L344" s="3"/>
       <c r="M344" s="3"/>
       <c r="N344" s="3"/>
-    </row>
-    <row r="345" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O344" s="3"/>
+    </row>
+    <row r="345" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>156</v>
       </c>
@@ -15260,14 +17110,20 @@
       <c r="I345" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J345" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K345" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L345" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L345" s="3"/>
       <c r="M345" s="3"/>
       <c r="N345" s="3"/>
-    </row>
-    <row r="346" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O345" s="3"/>
+    </row>
+    <row r="346" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>156</v>
       </c>
@@ -15295,14 +17151,20 @@
       <c r="I346" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J346" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K346" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L346" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L346" s="3"/>
       <c r="M346" s="3"/>
       <c r="N346" s="3"/>
-    </row>
-    <row r="347" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O346" s="3"/>
+    </row>
+    <row r="347" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>156</v>
       </c>
@@ -15330,14 +17192,20 @@
       <c r="I347" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J347" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K347" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L347" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L347" s="3"/>
       <c r="M347" s="3"/>
       <c r="N347" s="3"/>
-    </row>
-    <row r="348" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O347" s="3"/>
+    </row>
+    <row r="348" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>156</v>
       </c>
@@ -15365,14 +17233,20 @@
       <c r="I348" s="2" t="s">
         <v>659</v>
       </c>
+      <c r="J348" s="2" t="s">
+        <v>867</v>
+      </c>
       <c r="K348" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L348" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="L348" s="3"/>
       <c r="M348" s="3"/>
       <c r="N348" s="3"/>
-    </row>
-    <row r="349" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O348" s="3"/>
+    </row>
+    <row r="349" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>156</v>
       </c>
@@ -15400,11 +17274,17 @@
       <c r="I349" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="L349" s="3"/>
+      <c r="J349" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="K349" s="2" t="s">
+        <v>890</v>
+      </c>
       <c r="M349" s="3"/>
       <c r="N349" s="3"/>
-    </row>
-    <row r="350" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O349" s="3"/>
+    </row>
+    <row r="350" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>157</v>
       </c>
@@ -15414,12 +17294,12 @@
       <c r="C350" s="1">
         <v>15701</v>
       </c>
-      <c r="L350" s="6"/>
       <c r="M350" s="6"/>
       <c r="N350" s="6"/>
+      <c r="O350" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K350" xr:uid="{21E7D8C5-59DB-465F-80B7-E6C364678A90}"/>
+  <autoFilter ref="A1:L350" xr:uid="{21E7D8C5-59DB-465F-80B7-E6C364678A90}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/inst/resources/reference_indicator_bank.xlsx
+++ b/inst/resources/reference_indicator_bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0968C-A523-4925-868B-696C113DECB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA07700E-2BCA-4D4E-9B43-017FA16CFC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
+    <workbookView xWindow="-14970" yWindow="120" windowWidth="14955" windowHeight="15360" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_bank" sheetId="2" r:id="rId1"/>
@@ -3228,6 +3228,9 @@
       <c r="C2" s="2">
         <v>10101</v>
       </c>
+      <c r="D2" s="2">
+        <v>10000</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3272,6 +3275,9 @@
       <c r="C3" s="2">
         <v>10102</v>
       </c>
+      <c r="D3" s="2">
+        <v>10000</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
@@ -3316,6 +3322,9 @@
       <c r="C4" s="2">
         <v>10103</v>
       </c>
+      <c r="D4" s="2">
+        <v>10102</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3403,6 +3412,9 @@
       </c>
       <c r="C6" s="2">
         <v>10105</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10000</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
